--- a/vital_score_reference.xlsx
+++ b/vital_score_reference.xlsx
@@ -1,31 +1,84 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/troykettle/Documents/01_Repositories/Fuzzy_EWS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1908DCBD-3450-2748-B0C3-C3FDF1A13E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5209BA-2154-5E4F-83EC-99944985120F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19820" yWindow="-28200" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Heart Rate" sheetId="2" r:id="rId1"/>
-    <sheet name="Blood Pressure" sheetId="3" r:id="rId2"/>
-    <sheet name="Temperature" sheetId="4" r:id="rId3"/>
-    <sheet name="Respiratory Rate" sheetId="5" r:id="rId4"/>
-    <sheet name="Oxygen Saturation" sheetId="6" r:id="rId5"/>
-    <sheet name="Inspired Oxygen" sheetId="7" r:id="rId6"/>
+    <sheet name="Overview" sheetId="1" r:id="rId1"/>
+    <sheet name="Heart Rate" sheetId="2" r:id="rId2"/>
+    <sheet name="Blood Pressure" sheetId="3" r:id="rId3"/>
+    <sheet name="Temperature" sheetId="4" r:id="rId4"/>
+    <sheet name="Respiratory Rate" sheetId="5" r:id="rId5"/>
+    <sheet name="Oxygen Saturation" sheetId="6" r:id="rId6"/>
+    <sheet name="Supplementary Oxygen" sheetId="7" r:id="rId7"/>
+    <sheet name="Inspired Oxygen (FiO2)" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="44">
+  <si>
+    <t>Fuzzy EWS — Per-Vital Score Reference</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>What it covers</t>
+  </si>
+  <si>
+    <t>Heart Rate</t>
+  </si>
+  <si>
+    <t>NEWS-2 Heart Rate (Scale 1): ≤40→3, 41-50→1, 51-90→0, 91-110→1, 111-130→2, ≥131→3.</t>
+  </si>
+  <si>
+    <t>Blood Pressure</t>
+  </si>
+  <si>
+    <t>Systolic BP — asymmetric (Tab 4) fuzzy scoring. Hypotensive side unchanged: ≤90→3, 91-100→2, 101-110→1. Above normal: mild-raised and moderately-raised fuzzy sets are merged into a single 'elevated' set mapped to Mild concern only — Moderate concern is never fired from the upper side. Only a hypertensive crisis (≥220 mmHg) reaches Severe concern. NEWS-2 column (unchanged): ≤90→3, 91-100→2, 101-110→1, 111-219→0, ≥220→3.</t>
+  </si>
+  <si>
+    <t>Temperature</t>
+  </si>
+  <si>
+    <t>NEWS-2 Temperature (Scale 1): ≤35.0→3, 35.1-36.0→1, 36.1-38.0→0, 38.1-39.0→1, ≥39.1→2.</t>
+  </si>
+  <si>
+    <t>Respiratory Rate</t>
+  </si>
+  <si>
+    <t>NEWS-2 Respiratory Rate (Scale 1): ≤8→3, 9-11→1, 12-20→0, 21-24→2, ≥25→3.</t>
+  </si>
+  <si>
+    <t>Oxygen Saturation</t>
+  </si>
+  <si>
+    <t>NEWS-2 SpO2 (Scale 1): ≤91→3, 92-93→2, 94-95→1, ≥96→0.</t>
+  </si>
+  <si>
+    <t>Supplementary Oxygen</t>
+  </si>
+  <si>
+    <t>Supplementary oxygen flow rate (nasal cannula, L/min). Membership functions derived directly from Part 1 training-data event rates using Gaussian CDF transitions (no FiO₂ conversion formula). Transition centres: No concern→Mild at 2 L/min, Mild→Moderate at 5 L/min, Moderate→Severe at 9 L/min. NEWS-2: 0 L/min (room air) → 0 points; any supplemental flow &gt; 0 → +2 points.</t>
+  </si>
+  <si>
+    <t>Inspired Oxygen (FiO2)</t>
+  </si>
+  <si>
+    <t>Inspired oxygen concentration (% FiO2) directly from the generated membership functions (21–100%). NEWS-2 has no per-value FiO2 score; it adds +2 whenever the patient is on supplemental oxygen (FiO2 &gt; 21%). This column shows that flag: 0 at 21%, 2 above.</t>
+  </si>
   <si>
     <t>Heart Rate — NEWS-2 vs Snapshot Fuzzy Score (SS)</t>
   </si>
@@ -72,6 +125,9 @@
     <t>Input (mmHg)</t>
   </si>
   <si>
+    <t>Above normal - elevated</t>
+  </si>
+  <si>
     <t>Temperature — NEWS-2 vs Snapshot Fuzzy Score (SS)</t>
   </si>
   <si>
@@ -90,13 +146,19 @@
     <t>Input (%)</t>
   </si>
   <si>
-    <t>Inspired Oxygen — NEWS-2 vs Snapshot Fuzzy Score (SS)</t>
+    <t>Supplementary Oxygen — NEWS-2 vs Snapshot Fuzzy Score (SS)</t>
+  </si>
+  <si>
+    <t>Input (L/min)</t>
+  </si>
+  <si>
+    <t>NEWS-2 (supp. O2 flag)</t>
+  </si>
+  <si>
+    <t>Inspired Oxygen (FiO2) — NEWS-2 vs Snapshot Fuzzy Score (SS)</t>
   </si>
   <si>
     <t>Input (% FiO2)</t>
-  </si>
-  <si>
-    <t>NEWS-2 (supp. O2 flag)</t>
   </si>
 </sst>
 </file>
@@ -107,7 +169,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +187,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF1F3A5F"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -173,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -203,6 +271,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -505,6 +574,93 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10"/>
+    </row>
+    <row r="4" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="64" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="64" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="48" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -517,8 +673,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
+      <c r="A1" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -527,19 +683,19 @@
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -553,7 +709,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E4" s="5">
         <v>0.99999999999999956</v>
@@ -570,7 +726,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E5" s="7">
         <v>0.99999999999999845</v>
@@ -587,7 +743,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E6" s="5">
         <v>0.99999999999999201</v>
@@ -604,7 +760,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E7" s="7">
         <v>0.99999999999995981</v>
@@ -621,7 +777,7 @@
         <v>2.7533333333333321</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E8" s="5">
         <v>0.99999999999980638</v>
@@ -638,7 +794,7 @@
         <v>2.7533333333333272</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E9" s="7">
         <v>0.99999999999910705</v>
@@ -655,7 +811,7 @@
         <v>2.7533333333333081</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E10" s="5">
         <v>0.99999999999605738</v>
@@ -672,7 +828,7 @@
         <v>2.7533333333332251</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E11" s="7">
         <v>0.99999999998332645</v>
@@ -689,7 +845,7 @@
         <v>2.7533333333328951</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E12" s="5">
         <v>0.99999999993245803</v>
@@ -706,7 +862,7 @@
         <v>2.7533333333316321</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E13" s="7">
         <v>0.99999999973791798</v>
@@ -723,7 +879,7 @@
         <v>2.75333333332701</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E14" s="5">
         <v>0.99999999902580605</v>
@@ -740,7 +896,7 @@
         <v>2.7533333333108141</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E15" s="7">
         <v>0.99999999653084037</v>
@@ -757,7 +913,7 @@
         <v>2.7533333332565029</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E16" s="5">
         <v>0.99999998816405444</v>
@@ -774,7 +930,7 @@
         <v>2.7533333330821792</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E17" s="7">
         <v>0.99999996130870805</v>
@@ -791,7 +947,7 @@
         <v>2.7533333325466192</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E18" s="5">
         <v>0.99999987880352736</v>
@@ -808,7 +964,7 @@
         <v>2.7533333309717758</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E19" s="7">
         <v>0.99999963619259824</v>
@@ -825,7 +981,7 @@
         <v>2.7533333265393112</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E20" s="5">
         <v>0.99999895335334277</v>
@@ -842,7 +998,7 @@
         <v>2.753333314598529</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E21" s="7">
         <v>0.99999711382759882</v>
@@ -859,7 +1015,7 @@
         <v>2.753333283809229</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E22" s="5">
         <v>0.99999237061258239</v>
@@ -876,7 +1032,7 @@
         <v>2.7533332078209249</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E23" s="7">
         <v>0.99998066431452703</v>
@@ -893,7 +1049,7 @@
         <v>2.7533330283169568</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E24" s="5">
         <v>0.99995301104885104</v>
@@ -910,7 +1066,7 @@
         <v>2.7533326224513379</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E25" s="7">
         <v>0.99989048606231645</v>
@@ -927,7 +1083,7 @@
         <v>2.7533317440918932</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E26" s="5">
         <v>0.99975517249068524</v>
@@ -944,7 +1100,7 @@
         <v>2.7533299246190741</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E27" s="7">
         <v>0.99947488100595561</v>
@@ -961,7 +1117,7 @@
         <v>2.7533263171328288</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E28" s="5">
         <v>0.99891915661186637</v>
@@ -978,7 +1134,7 @@
         <v>2.7533194708654181</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E29" s="7">
         <v>0.99786455062904578</v>
@@ -995,7 +1151,7 @@
         <v>2.753307034313722</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E30" s="5">
         <v>0.99594896132350141</v>
@@ -1012,7 +1168,7 @@
         <v>2.7532854094341932</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E31" s="7">
         <v>0.9926185631618224</v>
@@ -1029,7 +1185,7 @@
         <v>2.7532494153919109</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E32" s="5">
         <v>0.98707649759321037</v>
@@ -1046,7 +1202,7 @@
         <v>2.753139565189235</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E33" s="7">
         <v>0.97824917371295639</v>
@@ -1063,7 +1219,7 @@
         <v>2.7529168772204118</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E34" s="5">
         <v>0.96479154618581342</v>
@@ -1080,7 +1236,7 @@
         <v>2.62833779986516</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E35" s="7">
         <v>0.94515386907542476</v>
@@ -1097,7 +1253,7 @@
         <v>2.57790584176119</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E36" s="5">
         <v>0.91772587739737799</v>
@@ -1114,7 +1270,7 @@
         <v>2.5198276492271492</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E37" s="7">
         <v>0.88105846290143519</v>
@@ -1131,7 +1287,7 @@
         <v>2.4577519190787158</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E38" s="5">
         <v>0.8341394312559498</v>
@@ -1148,7 +1304,7 @@
         <v>2.395824867871291</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E39" s="7">
         <v>0.77667483745570198</v>
@@ -1165,7 +1321,7 @@
         <v>2.337773064033247</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E40" s="5">
         <v>0.70930984696074839</v>
@@ -1182,7 +1338,7 @@
         <v>2.2859975633260281</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E41" s="7">
         <v>0.63372220035181182</v>
@@ -1199,7 +1355,7 @@
         <v>2.2394560625076152</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E42" s="5">
         <v>0.55254200541300713</v>
@@ -1216,7 +1372,7 @@
         <v>2.1968666769123208</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E43" s="7">
         <v>0.51692836491172156</v>
@@ -1233,7 +1389,7 @@
         <v>2.157380649332759</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E44" s="5">
         <v>0.58979502341673684</v>
@@ -1250,7 +1406,7 @@
         <v>2.1206616343626949</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E45" s="7">
         <v>0.65319876766214879</v>
@@ -1267,7 +1423,7 @@
         <v>1.9986721071864391</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E46" s="5">
         <v>0.70279917285072335</v>
@@ -1284,7 +1440,7 @@
         <v>1.9361758942433509</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E47" s="7">
         <v>0.73512034979150065</v>
@@ -1301,7 +1457,7 @@
         <v>1.8713595889021131</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E48" s="5">
         <v>0.74789218257816314</v>
@@ -1318,7 +1474,7 @@
         <v>1.805110948623291</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E49" s="7">
         <v>0.74025784637182923</v>
@@ -1335,7 +1491,7 @@
         <v>1.738837031065672</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E50" s="5">
         <v>0.71283946493521544</v>
@@ -1352,7 +1508,7 @@
         <v>1.660488915642981</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E51" s="7">
         <v>0.6676652347076647</v>
@@ -1369,7 +1525,7 @@
         <v>1.6031990876873781</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E52" s="5">
         <v>0.60796636127422665</v>
@@ -1386,7 +1542,7 @@
         <v>1.54704301954748</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E53" s="7">
         <v>0.5378575997936822</v>
@@ -1403,7 +1559,7 @@
         <v>1.491415644618368</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E54" s="5">
         <v>0.4836195357569727</v>
@@ -1420,7 +1576,7 @@
         <v>1.410030285310524</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E55" s="7">
         <v>0.54209537955598819</v>
@@ -1437,7 +1593,7 @@
         <v>1.340162687799074</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E56" s="5">
         <v>0.58834318244762274</v>
@@ -1454,7 +1610,7 @@
         <v>1.2650976730390471</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E57" s="7">
         <v>0.6185442632676923</v>
@@ -1471,7 +1627,7 @@
         <v>1.1861976619992409</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E58" s="5">
         <v>0.6301786444441233</v>
@@ -1488,7 +1644,7 @@
         <v>1.1055192105021809</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E59" s="7">
         <v>0.62235306852404659</v>
@@ -1505,7 +1661,7 @@
         <v>1.0253814704072171</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E60" s="5">
         <v>0.59589910508789068</v>
@@ -1522,7 +1678,7 @@
         <v>0.94866495327903611</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E61" s="7">
         <v>0.55323116177077936</v>
@@ -1539,7 +1695,7 @@
         <v>0.80248911070560103</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E62" s="5">
         <v>0.49799700447962642</v>
@@ -1556,7 +1712,7 @@
         <v>0.76309407771907289</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E63" s="7">
         <v>0.53878245587066642</v>
@@ -1573,7 +1729,7 @@
         <v>0.72048152943685884</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E64" s="5">
         <v>0.61620814631116305</v>
@@ -1590,7 +1746,7 @@
         <v>0.6736019582195284</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E65" s="7">
         <v>0.6892434694912859</v>
@@ -1607,7 +1763,7 @@
         <v>0.62108821801544045</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E66" s="5">
         <v>0.75549273517198545</v>
@@ -1624,7 +1780,7 @@
         <v>0.56422753827119354</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E67" s="7">
         <v>0.81327961506936863</v>
@@ -1641,7 +1797,7 @@
         <v>0.5058029423735011</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E68" s="5">
         <v>0.86175006665915932</v>
@@ -1658,7 +1814,7 @@
         <v>0.44916275227174851</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E69" s="7">
         <v>0.9008452732763228</v>
@@ -1675,7 +1831,7 @@
         <v>0.39772796144544881</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E70" s="5">
         <v>0.93116784625598314</v>
@@ -1692,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E71" s="7">
         <v>0.95378292757575101</v>
@@ -1709,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E72" s="5">
         <v>0.97000112607859879</v>
@@ -1726,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E73" s="7">
         <v>0.98118347303153275</v>
@@ -1743,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E74" s="5">
         <v>0.98859420361355121</v>
@@ -1760,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E75" s="7">
         <v>0.99331076178377298</v>
@@ -1777,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E76" s="5">
         <v>0.99618670109237095</v>
@@ -1794,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E77" s="7">
         <v>0.99785470911617358</v>
@@ -1811,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E78" s="5">
         <v>0.998754138207399</v>
@@ -1828,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E79" s="7">
         <v>0.99916887521178044</v>
@@ -1845,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E80" s="5">
         <v>0.99926516043777636</v>
@@ -1862,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E81" s="7">
         <v>0.99912326718122135</v>
@@ -1879,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E82" s="5">
         <v>0.99876059019981522</v>
@@ -1896,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E83" s="7">
         <v>0.99814616977397885</v>
@@ -1913,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E84" s="5">
         <v>0.99720802522462881</v>
@@ -1930,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E85" s="7">
         <v>0.99583518714696118</v>
@@ -1947,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E86" s="5">
         <v>0.9938763568050476</v>
@@ -1964,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E87" s="7">
         <v>0.99113696809474361</v>
@@ -1981,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E88" s="5">
         <v>0.98737624959542503</v>
@@ -1998,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E89" s="7">
         <v>0.98230574169765361</v>
@@ -2015,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E90" s="5">
         <v>0.97559060284816024</v>
@@ -2032,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E91" s="7">
         <v>0.9668548880795238</v>
@@ -2049,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E92" s="5">
         <v>0.95569174272444679</v>
@@ -2066,7 +2222,7 @@
         <v>0.375801006557623</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E93" s="7">
         <v>0.9416790786358028</v>
@@ -2083,7 +2239,7 @@
         <v>0.4072288952154926</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E94" s="5">
         <v>0.92440077129771436</v>
@@ -2100,7 +2256,7 @@
         <v>0.44207004386980697</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E95" s="7">
         <v>0.90347275203190458</v>
@@ -2117,7 +2273,7 @@
         <v>0.47944910631649251</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E96" s="5">
         <v>0.87857262665729197</v>
@@ -2134,7 +2290,7 @@
         <v>0.51846655764363647</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E97" s="7">
         <v>0.84947072114133593</v>
@@ -2151,7 +2307,7 @@
         <v>0.55799397436960863</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E98" s="5">
         <v>0.81605984927817921</v>
@@ -2168,7 +2324,7 @@
         <v>0.59709950609816476</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E99" s="7">
         <v>0.77838073509041394</v>
@@ -2185,7 +2341,7 @@
         <v>0.63480661073309019</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E100" s="5">
         <v>0.73664000362904325</v>
@@ -2202,7 +2358,7 @@
         <v>0.67040005197489072</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E101" s="7">
         <v>0.6912180380145283</v>
@@ -2219,7 +2375,7 @@
         <v>0.70342445273459853</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E102" s="5">
         <v>0.64266478946498939</v>
@@ -2236,7 +2392,7 @@
         <v>0.73426380246899248</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E103" s="7">
         <v>0.59168275505399315</v>
@@ -2253,7 +2409,7 @@
         <v>0.76338772504028762</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E104" s="5">
         <v>0.53909767578841394</v>
@@ -2270,7 +2426,7 @@
         <v>0.79104376906649698</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E105" s="7">
         <v>0.48581887923271438</v>
@@ -2287,7 +2443,7 @@
         <v>0.81742950020837668</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E106" s="5">
         <v>0.52934459967840808</v>
@@ -2304,7 +2460,7 @@
         <v>0.84271017396271786</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E107" s="7">
         <v>0.57290947849918883</v>
@@ -2321,7 +2477,7 @@
         <v>0.95580175153291924</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E108" s="5">
         <v>0.61302472940772779</v>
@@ -2338,7 +2494,7 @@
         <v>0.99282836072292635</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E109" s="7">
         <v>0.64878722117959142</v>
@@ -2355,7 +2511,7 @@
         <v>1.0288229655175489</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E110" s="5">
         <v>0.67944032250862541</v>
@@ -2372,7 +2528,7 @@
         <v>1.0637979920113141</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E111" s="7">
         <v>0.70440141665181866</v>
@@ -2389,7 +2545,7 @@
         <v>1.097805982824599</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E112" s="5">
         <v>0.72327695475524689</v>
@@ -2406,7 +2562,7 @@
         <v>1.130906725882632</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E113" s="7">
         <v>0.73586504233809658</v>
@@ -2423,7 +2579,7 @@
         <v>1.1631444868142891</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E114" s="5">
         <v>0.74214676849311401</v>
@@ -2440,7 +2596,7 @@
         <v>1.1945722361447979</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E115" s="7">
         <v>0.74226842592980602</v>
@@ -2457,7 +2613,7 @@
         <v>1.2252665349678049</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E116" s="5">
         <v>0.736517338092747</v>
@@ -2474,7 +2630,7 @@
         <v>1.255218690351857</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E117" s="7">
         <v>0.72529417984316091</v>
@@ -2491,7 +2647,7 @@
         <v>1.297353575936012</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E118" s="5">
         <v>0.7090844862377883</v>
@@ -2508,7 +2664,7 @@
         <v>1.322686495557631</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E119" s="7">
         <v>0.68843157404295563</v>
@@ -2525,7 +2681,7 @@
         <v>1.3482722547813799</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E120" s="5">
         <v>0.66391246464097642</v>
@@ -2542,7 +2698,7 @@
         <v>1.373996200984517</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E121" s="7">
         <v>0.63611771170739273</v>
@@ -2559,7 +2715,7 @@
         <v>1.399751357287796</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E122" s="5">
         <v>0.6056354044720258</v>
@@ -2576,7 +2732,7 @@
         <v>1.4254292564539861</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E123" s="7">
         <v>0.57303911120994433</v>
@@ -2593,7 +2749,7 @@
         <v>1.451113524021526</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E124" s="5">
         <v>0.53887918718196515</v>
@@ -2610,7 +2766,7 @@
         <v>1.476822731214825</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E125" s="7">
         <v>0.50367670266699793</v>
@@ -2627,7 +2783,7 @@
         <v>1.5231789694629421</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E126" s="5">
         <v>0.47472138428948107</v>
@@ -2644,7 +2800,7 @@
         <v>1.552113136696498</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E127" s="7">
         <v>0.50353676996533592</v>
@@ -2661,7 +2817,7 @@
         <v>1.58173045299892</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E128" s="5">
         <v>0.53095045108621486</v>
@@ -2678,7 +2834,7 @@
         <v>1.612134556685507</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E129" s="7">
         <v>0.55662082693779646</v>
@@ -2695,7 +2851,7 @@
         <v>1.6434483102674</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E130" s="5">
         <v>0.5802310901318577</v>
@@ -2712,7 +2868,7 @@
         <v>1.67549352543373</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E131" s="7">
         <v>0.60149644864778384</v>
@@ -2729,7 +2885,7 @@
         <v>1.7080558689976431</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E132" s="5">
         <v>0.62017023292906504</v>
@@ -2746,7 +2902,7 @@
         <v>1.740979572474026</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E133" s="7">
         <v>0.6360486932098609</v>
@@ -2763,7 +2919,7 @@
         <v>1.7740445875558499</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E134" s="5">
         <v>0.64897436238214579</v>
@@ -2780,7 +2936,7 @@
         <v>1.807033286895368</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E135" s="7">
         <v>0.65883793315994388</v>
@@ -2797,7 +2953,7 @@
         <v>1.8397325458987539</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E136" s="5">
         <v>0.66557867009207738</v>
@@ -2814,7 +2970,7 @@
         <v>1.871917999700869</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E137" s="7">
         <v>0.66918344257305429</v>
@@ -2831,7 +2987,7 @@
         <v>1.903340409883868</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E138" s="5">
         <v>0.66968452062244643</v>
@@ -2848,7 +3004,7 @@
         <v>1.933883521624475</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E139" s="7">
         <v>0.66715631808806464</v>
@@ -2865,7 +3021,7 @@
         <v>1.963337725417901</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E140" s="5">
         <v>0.66171129648828053</v>
@@ -2882,7 +3038,7 @@
         <v>1.991665347866479</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E141" s="7">
         <v>0.65349525655396057</v>
@@ -2899,7 +3055,7 @@
         <v>2.0187871441741221</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E142" s="5">
         <v>0.64268224438913335</v>
@@ -2916,7 +3072,7 @@
         <v>2.127257537125478</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E143" s="7">
         <v>0.62946928671552393</v>
@@ -2933,7 +3089,7 @@
         <v>2.138547330066527</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E144" s="5">
         <v>0.61407114727840151</v>
@@ -2950,7 +3106,7 @@
         <v>2.1501419408322211</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E145" s="7">
         <v>0.59671526697720401</v>
@@ -2967,7 +3123,7 @@
         <v>2.1619869124284361</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E146" s="5">
         <v>0.57763701659728783</v>
@@ -2984,7 +3140,7 @@
         <v>2.1740970226944909</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E147" s="7">
         <v>0.55707535599757152</v>
@@ -3001,7 +3157,7 @@
         <v>2.1864932120101219</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E148" s="5">
         <v>0.53526895976091815</v>
@@ -3018,7 +3174,7 @@
         <v>2.1992037044832911</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E149" s="7">
         <v>0.5124528386609063</v>
@@ -3035,7 +3191,7 @@
         <v>2.2122433175562288</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E150" s="5">
         <v>0.50030704827666506</v>
@@ -3052,7 +3208,7 @@
         <v>2.2256411563935972</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E151" s="7">
         <v>0.52684643240037377</v>
@@ -3069,7 +3225,7 @@
         <v>2.2394281046805302</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E152" s="5">
         <v>0.55326713721444376</v>
@@ -3086,7 +3242,7 @@
         <v>2.2536455754646498</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E153" s="7">
         <v>0.57945341442871123</v>
@@ -3103,7 +3259,7 @@
         <v>2.2683120269095158</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E154" s="5">
         <v>0.6052926063042493</v>
@@ -3120,7 +3276,7 @@
         <v>2.2834565233827488</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E155" s="7">
         <v>0.63067659679048516</v>
@@ -3137,7 +3293,7 @@
         <v>2.2991056410771011</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E156" s="5">
         <v>0.65550316376524242</v>
@@ -3154,7 +3310,7 @@
         <v>2.315328089894042</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E157" s="7">
         <v>0.67967720429710332</v>
@@ -3171,7 +3327,7 @@
         <v>2.3322852216285002</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E158" s="5">
         <v>0.70311180867287382</v>
@@ -3188,7 +3344,7 @@
         <v>2.349953882785885</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E159" s="7">
         <v>0.72572916342161609</v>
@@ -3205,7 +3361,7 @@
         <v>2.368238425754873</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E160" s="5">
         <v>0.74746126854974848</v>
@@ -3222,7 +3378,7 @@
         <v>2.3870856543445651</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E161" s="7">
         <v>0.76825045949293158</v>
@@ -3239,7 +3395,7 @@
         <v>2.4063742033011399</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E162" s="5">
         <v>0.78804972969695564</v>
@@ -3256,7 +3412,7 @@
         <v>2.4260215245102481</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E163" s="7">
         <v>0.80682285507048634</v>
@@ -3273,7 +3429,7 @@
         <v>2.445876643128237</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E164" s="5">
         <v>0.82454432662621713</v>
@@ -3290,7 +3446,7 @@
         <v>2.4658352129064829</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E165" s="7">
         <v>0.84119910227999939</v>
@@ -3307,7 +3463,7 @@
         <v>2.485765282104424</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E166" s="5">
         <v>0.85678219286987622</v>
@@ -3324,7 +3480,7 @@
         <v>2.5055138638468049</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E167" s="7">
         <v>0.87129810087723358</v>
@@ -3341,7 +3497,7 @@
         <v>2.5249452136985129</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E168" s="5">
         <v>0.88476013300094269</v>
@@ -3358,7 +3514,7 @@
         <v>2.543924337914834</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E169" s="7">
         <v>0.89718960960637717</v>
@@ -3375,7 +3531,7 @@
         <v>2.5623201637230828</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E170" s="5">
         <v>0.9086149951319632</v>
@@ -3392,7 +3548,7 @@
         <v>2.5800214705811189</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E171" s="7">
         <v>0.91907097380570724</v>
@@ -3409,7 +3565,7 @@
         <v>2.5969443129678318</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E172" s="5">
         <v>0.92859749455106277</v>
@@ -3426,7 +3582,7 @@
         <v>2.6129613613307101</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E173" s="7">
         <v>0.93723880781836699</v>
@@ -3443,7 +3599,7 @@
         <v>2.6280117810665748</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E174" s="5">
         <v>0.94504251535751982</v>
@@ -3460,7 +3616,7 @@
         <v>2.7526323510104249</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E175" s="7">
         <v>0.95205865175642423</v>
@@ -3477,7 +3633,7 @@
         <v>2.7527863132784849</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E176" s="5">
         <v>0.95833881402338683</v>
@@ -3494,7 +3650,7 @@
         <v>2.7529008229605938</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E177" s="7">
         <v>0.96393535270858421</v>
@@ -3511,7 +3667,7 @@
         <v>2.752993895427204</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E178" s="5">
         <v>0.96890063515591041</v>
@@ -3528,7 +3684,7 @@
         <v>2.7530760440720932</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E179" s="7">
         <v>0.9732863885612334</v>
@@ -3545,7 +3701,7 @@
         <v>2.7531254737725899</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E180" s="5">
         <v>0.97714312768473555</v>
@@ -3562,7 +3718,7 @@
         <v>2.753168486961338</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E181" s="7">
         <v>0.98051966940825019</v>
@@ -3579,7 +3735,7 @@
         <v>2.7532059656813068</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E182" s="5">
         <v>0.98346273391226158</v>
@@ -3596,7 +3752,7 @@
         <v>2.7532384790896809</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E183" s="7">
         <v>0.98601663012357044</v>
@@ -3613,7 +3769,7 @@
         <v>2.7532568625786848</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E184" s="5">
         <v>0.98822302128853956</v>
@@ -3630,7 +3786,7 @@
         <v>2.753269188289869</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E185" s="7">
         <v>0.99012076507691205</v>
@@ -3647,7 +3803,7 @@
         <v>2.7532797419374262</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E186" s="5">
         <v>0.99174582152086177</v>
@@ -3664,7 +3820,7 @@
         <v>2.7532887384635938</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E187" s="7">
         <v>0.99313122133319476</v>
@@ -3681,7 +3837,7 @@
         <v>2.7532963737977232</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E188" s="5">
         <v>0.99430708670636558</v>
@@ -3698,7 +3854,7 @@
         <v>2.7533028253100031</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E189" s="7">
         <v>0.99530069654021758</v>
@@ -3715,7 +3871,7 @@
         <v>2.753308252495914</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E190" s="5">
         <v>0.9961365881447688</v>
@@ -3732,7 +3888,7 @@
         <v>2.7533127978427441</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E191" s="7">
         <v>0.99683668777468204</v>
@@ -3749,7 +3905,7 @@
         <v>2.7533165878325341</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E192" s="5">
         <v>0.99742046283219299</v>
@@ -3766,7 +3922,7 @@
         <v>2.7533197340397182</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E193" s="7">
         <v>0.99790508918344623</v>
@@ -3783,7 +3939,7 @@
         <v>2.7533223342860551</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E194" s="5">
         <v>0.99830562772942644</v>
@@ -3800,7 +3956,7 @@
         <v>2.753324473820304</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E195" s="7">
         <v>0.99863520512024517</v>
@@ -3817,7 +3973,7 @@
         <v>2.753326226494881</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E196" s="5">
         <v>0.99890519426784685</v>
@@ -3834,7 +3990,7 @@
         <v>2.7533276559166211</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E197" s="7">
         <v>0.99912539106943421</v>
@@ -3851,7 +4007,7 @@
         <v>2.7533288165533869</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E198" s="5">
         <v>0.99930418447935521</v>
@@ -3868,7 +4024,7 @@
         <v>2.7533297547825581</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E199" s="7">
         <v>0.99944871774323418</v>
@@ -3885,7 +4041,7 @@
         <v>2.7533305098714038</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E200" s="5">
         <v>0.99956503922208517</v>
@@ -3902,7 +4058,7 @@
         <v>2.7533311148828168</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E201" s="7">
         <v>0.99965824177787421</v>
@@ -3919,7 +4075,7 @@
         <v>2.7533315975028669</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E202" s="5">
         <v>0.99973259016134675</v>
@@ -3936,7 +4092,7 @@
         <v>2.7533319807892109</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E203" s="7">
         <v>0.99979163623726963</v>
@@ -3953,7 +4109,7 @@
         <v>2.7533322838414178</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E204" s="5">
         <v>0.99983832220361879</v>
@@ -3970,7 +4126,7 @@
         <v>2.7533325223959162</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E205" s="7">
         <v>0.99987507221401961</v>
@@ -3987,7 +4143,7 @@
         <v>2.7533327093494919</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E206" s="5">
         <v>0.99990387300276062</v>
@@ -4004,7 +4160,7 @@
         <v>2.753332855216108</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E207" s="7">
         <v>0.99992634424586879</v>
@@ -4021,7 +4177,7 @@
         <v>2.753332968522384</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E208" s="5">
         <v>0.99994379947750145</v>
@@ -4038,7 +4194,7 @@
         <v>2.753333056147365</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E209" s="7">
         <v>0.99995729842585379</v>
@@ -4055,7 +4211,7 @@
         <v>2.7533331236122489</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E210" s="5">
         <v>0.9999676916443212</v>
@@ -4072,7 +4228,7 @@
         <v>2.753333175325698</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E211" s="7">
         <v>0.99997565829873236</v>
@@ -4089,7 +4245,7 @@
         <v>2.7533332147900569</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E212" s="5">
         <v>0.99998173793645417</v>
@@ -4106,7 +4262,7 @@
         <v>2.7533332447735659</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E213" s="7">
         <v>0.99998635701369676</v>
@@ -4123,7 +4279,7 @@
         <v>2.753333267453181</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E214" s="5">
         <v>0.99998985089824055</v>
@@ -4140,7 +4296,7 @@
         <v>2.753333284532272</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E215" s="7">
         <v>0.99999248200018198</v>
@@ -4157,7 +4313,7 @@
         <v>2.7533332973369791</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E216" s="5">
         <v>0.99999445461640901</v>
@@ -4174,7 +4330,7 @@
         <v>2.7533333068946102</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E217" s="7">
         <v>0.99999592700799922</v>
@@ -4191,7 +4347,7 @@
         <v>2.7533333139970382</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E218" s="5">
         <v>0.99999702116553457</v>
@@ -4208,7 +4364,7 @@
         <v>2.7533333192516309</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E219" s="7">
         <v>0.99999783065683079</v>
@@ -4225,7 +4381,7 @@
         <v>2.753333323121955</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E220" s="5">
         <v>0.99999842689573737</v>
@@ -4242,7 +4398,7 @@
         <v>2.7533333259600772</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E221" s="7">
         <v>0.99999886411998617</v>
@@ -4259,7 +4415,7 @@
         <v>2.753333328032082</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E222" s="5">
         <v>0.99999918332078441</v>
@@ -4276,7 +4432,7 @@
         <v>2.7533333295380871</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E223" s="7">
         <v>0.99999941532693482</v>
@@ -4293,7 +4449,7 @@
         <v>2.7533333306278638</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E224" s="5">
         <v>0.9999995832115216</v>
@@ -4307,7 +4463,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E254"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -4320,8 +4476,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>13</v>
+      <c r="A1" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -4330,19 +4486,19 @@
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -4356,7 +4512,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E4" s="5">
         <v>1</v>
@@ -4373,7 +4529,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E5" s="7">
         <v>1</v>
@@ -4390,7 +4546,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E6" s="5">
         <v>0.99999999999999978</v>
@@ -4407,7 +4563,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E7" s="7">
         <v>0.99999999999999944</v>
@@ -4424,7 +4580,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E8" s="5">
         <v>0.99999999999999878</v>
@@ -4441,7 +4597,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E9" s="7">
         <v>0.99999999999999678</v>
@@ -4458,7 +4614,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E10" s="5">
         <v>0.99999999999999201</v>
@@ -4475,7 +4631,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E11" s="7">
         <v>0.99999999999998124</v>
@@ -4492,7 +4648,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E12" s="5">
         <v>0.99999999999995559</v>
@@ -4509,7 +4665,7 @@
         <v>2.7533333333333321</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E13" s="7">
         <v>0.99999999999989719</v>
@@ -4526,7 +4682,7 @@
         <v>2.7533333333333321</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E14" s="5">
         <v>0.99999999999976519</v>
@@ -4543,7 +4699,7 @@
         <v>2.7533333333333299</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E15" s="7">
         <v>0.99999999999946965</v>
@@ -4560,7 +4716,7 @@
         <v>2.753333333333325</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E16" s="5">
         <v>0.99999999999881584</v>
@@ -4577,7 +4733,7 @@
         <v>2.7533333333333161</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E17" s="7">
         <v>0.99999999999738876</v>
@@ -4594,7 +4750,7 @@
         <v>2.753333333333297</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E18" s="5">
         <v>0.99999999999431155</v>
@@ -4611,7 +4767,7 @@
         <v>2.7533333333332539</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E19" s="7">
         <v>0.99999999998775879</v>
@@ -4628,7 +4784,7 @@
         <v>2.7533333333331642</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E20" s="5">
         <v>0.99999999997397637</v>
@@ -4645,7 +4801,7 @@
         <v>2.753333333332979</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E21" s="7">
         <v>0.99999999994534483</v>
@@ -4662,7 +4818,7 @@
         <v>2.7533333333325971</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E22" s="5">
         <v>0.99999999988660104</v>
@@ -4679,7 +4835,7 @@
         <v>2.753333333331824</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E23" s="7">
         <v>0.9999999997675616</v>
@@ -4696,7 +4852,7 @@
         <v>2.7533333333302781</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E24" s="5">
         <v>0.99999999952931484</v>
@@ -4713,7 +4869,7 @@
         <v>2.753333333327221</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E25" s="7">
         <v>0.99999999905836778</v>
@@ -4730,7 +4886,7 @@
         <v>2.753333333321252</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E26" s="5">
         <v>0.99999999813892404</v>
@@ -4747,7 +4903,7 @@
         <v>2.7533333333097438</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E27" s="7">
         <v>0.99999999636601344</v>
@@ -4764,7 +4920,7 @@
         <v>2.7533333332878271</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E28" s="5">
         <v>0.99999999298959141</v>
@@ -4781,7 +4937,7 @@
         <v>2.753333333246601</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E29" s="7">
         <v>0.99999998663869605</v>
@@ -4798,7 +4954,7 @@
         <v>2.7533333331700161</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E30" s="5">
         <v>0.99999997484033798</v>
@@ -4815,7 +4971,7 @@
         <v>2.7533333330294938</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E31" s="7">
         <v>0.99999995319240043</v>
@@ -4832,7 +4988,7 @@
         <v>2.7533333327748419</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E32" s="5">
         <v>0.99999991396226118</v>
@@ -4849,7 +5005,7 @@
         <v>2.753333332319059</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E33" s="7">
         <v>0.99999984374699635</v>
@@ -4866,7 +5022,7 @@
         <v>2.7533333315133501</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E34" s="5">
         <v>0.99999971962418843</v>
@@ -4883,7 +5039,7 @@
         <v>2.7533333301066332</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E35" s="7">
         <v>0.99999950291365525</v>
@@ -4900,7 +5056,7 @@
         <v>2.7533333276808949</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E36" s="5">
         <v>0.99999912921905243</v>
@@ -4917,7 +5073,7 @@
         <v>2.7533333235495752</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E37" s="7">
         <v>0.99999849277239317</v>
@@ -4934,7 +5090,7 @@
         <v>2.7533333166002518</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E38" s="5">
         <v>0.99999742220113297</v>
@@ -4951,7 +5107,7 @@
         <v>2.7533333050549711</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E39" s="7">
         <v>0.99999564360420679</v>
@@ -4968,7 +5124,7 @@
         <v>2.7533332861108311</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E40" s="5">
         <v>0.99999272518358517</v>
@@ -4985,7 +5141,7 @@
         <v>2.7533332554097472</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E41" s="7">
         <v>0.99998799555946039</v>
@@ -5002,7 +5158,7 @@
         <v>2.7533332062690858</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E42" s="5">
         <v>0.99998042524765463</v>
@@ -5019,7 +5175,7 @@
         <v>2.7533331285841589</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E43" s="7">
         <v>0.99996845758583841</v>
@@ -5036,7 +5192,7 @@
         <v>2.7533330072896738</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E44" s="5">
         <v>0.99994977171884902</v>
@@ -5053,7 +5209,7 @@
         <v>2.7533328202412939</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E45" s="7">
         <v>0.99992095625566479</v>
@@ -5070,7 +5226,7 @@
         <v>2.7533325353523841</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E46" s="5">
         <v>0.99987706819741518</v>
@@ -5087,7 +5243,7 @@
         <v>2.753332106797969</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E47" s="7">
         <v>0.99981104819417355</v>
@@ -5104,7 +5260,7 @@
         <v>2.7533314700824429</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E48" s="5">
         <v>0.99971296081477479</v>
@@ -5121,7 +5277,7 @@
         <v>2.75333053576552</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E49" s="7">
         <v>0.99956902822478877</v>
@@ -5138,7 +5294,7 @@
         <v>2.753329181659486</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E50" s="5">
         <v>0.99936042857735041</v>
@@ -5155,7 +5311,7 @@
         <v>2.7533272433580218</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E51" s="7">
         <v>0.99906183777666702</v>
@@ -5172,7 +5328,7 @@
         <v>2.7533245030407998</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E52" s="5">
         <v>0.99863970633331878</v>
@@ -5189,7 +5345,7 @@
         <v>2.7533206766254592</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E53" s="7">
         <v>0.99805028288286679</v>
@@ -5206,7 +5362,7 @@
         <v>2.7533153995139048</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E54" s="5">
         <v>0.99723742326468801</v>
@@ -5223,7 +5379,7 @@
         <v>2.753308211402631</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E55" s="7">
         <v>0.99613025884597195</v>
@@ -5240,7 +5396,7 @@
         <v>2.7532985408904351</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E56" s="5">
         <v>0.99464083903305156</v>
@@ -5257,7 +5413,7 @@
         <v>2.753285690907068</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E57" s="7">
         <v>0.99266190840452595</v>
@@ -5274,7 +5430,7 @@
         <v>2.7532688262795082</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E58" s="5">
         <v>0.99006502498886795</v>
@@ -5291,7 +5447,7 @@
         <v>2.7532469650168321</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E59" s="7">
         <v>0.98669926784376039</v>
@@ -5308,7 +5464,7 @@
         <v>2.7531923165533638</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E60" s="5">
         <v>0.98239081302810438</v>
@@ -5325,7 +5481,7 @@
         <v>2.7531229324406268</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E61" s="7">
         <v>0.9769436703194988</v>
@@ -5342,7 +5498,7 @@
         <v>2.753017150364875</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E62" s="5">
         <v>0.97014186166803285</v>
@@ -5359,7 +5515,7 @@
         <v>2.7528598976609802</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E63" s="7">
         <v>0.96175328043358643</v>
@@ -5376,7 +5532,7 @@
         <v>2.7526195137933498</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E64" s="5">
         <v>0.95153539408082277</v>
@@ -5393,7 +5549,7 @@
         <v>2.6168426689070809</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E65" s="7">
         <v>0.93924284157995197</v>
@@ -5410,7 +5566,7 @@
         <v>2.5899256791397001</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E66" s="5">
         <v>0.92463683380985795</v>
@@ -5427,7 +5583,7 @@
         <v>2.5606311261307648</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E67" s="7">
         <v>0.90749609900377759</v>
@@ -5444,7 +5600,7 @@
         <v>2.5294759420910879</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E68" s="5">
         <v>0.8876289386019407</v>
@@ -5461,7 +5617,7 @@
         <v>2.496980240898858</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E69" s="7">
         <v>0.86488578860800835</v>
@@ -5478,7 +5634,7 @@
         <v>2.463814392369132</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E70" s="5">
         <v>0.83917153700448799</v>
@@ -5495,7 +5651,7 @@
         <v>2.4306337616049811</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E71" s="7">
         <v>0.81045674867850215</v>
@@ -5512,7 +5668,7 @@
         <v>2.398041151391531</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E72" s="5">
         <v>0.77878691322236393</v>
@@ -5529,7 +5685,7 @@
         <v>2.3665443310252812</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E73" s="7">
         <v>0.74428887071420724</v>
@@ -5546,7 +5702,7 @@
         <v>2.336668733559625</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E74" s="5">
         <v>0.70717369184720313</v>
@@ -5563,7 +5719,7 @@
         <v>2.3086746829045568</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E75" s="7">
         <v>0.66773548848510678</v>
@@ -5580,7 +5736,7 @@
         <v>2.2825338879700499</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E76" s="5">
         <v>0.6263458964118247</v>
@@ -5597,7 +5753,7 @@
         <v>2.2577910697284431</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E77" s="7">
         <v>0.58344428249395208</v>
@@ -5614,7 +5770,7 @@
         <v>2.2342969693936801</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E78" s="5">
         <v>0.53952405563113759</v>
@@ -5631,7 +5787,7 @@
         <v>2.211901262173869</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E79" s="7">
         <v>0.49511577285761488</v>
@@ -5648,7 +5804,7 @@
         <v>2.1904427845129399</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E80" s="5">
         <v>0.51925567914606019</v>
@@ -5665,7 +5821,7 @@
         <v>2.1698083649246391</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E81" s="7">
         <v>0.5523223821269081</v>
@@ -5682,7 +5838,7 @@
         <v>2.0585400560374771</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E82" s="5">
         <v>0.58136151988997353</v>
@@ -5699,7 +5855,7 @@
         <v>2.0147584350844818</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E83" s="7">
         <v>0.60542884450796219</v>
@@ -5716,7 +5872,7 @@
         <v>1.9683997585923629</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E84" s="5">
         <v>0.6236653528677587</v>
@@ -5733,7 +5889,7 @@
         <v>1.9201518006484639</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E85" s="7">
         <v>0.635343909330226</v>
@@ -5750,7 +5906,7 @@
         <v>1.8704611350523099</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E86" s="5">
         <v>0.63991425025154114</v>
@@ -5767,7 +5923,7 @@
         <v>1.820023978811474</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E87" s="7">
         <v>0.63704284824337409</v>
@@ -5784,7 +5940,7 @@
         <v>1.769557440199915</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E88" s="5">
         <v>0.62664390206211806</v>
@@ -5801,7 +5957,7 @@
         <v>1.7198046347338121</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E89" s="7">
         <v>0.60889791377060032</v>
@@ -5818,7 +5974,7 @@
         <v>1.6714030869039069</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E90" s="5">
         <v>0.5842549845525199</v>
@@ -5835,7 +5991,7 @@
         <v>1.6247863590323759</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E91" s="7">
         <v>0.55342109923107685</v>
@@ -5852,7 +6008,7 @@
         <v>1.5803666477223219</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E92" s="5">
         <v>0.51732718753569307</v>
@@ -5869,7 +6025,7 @@
         <v>1.5378607344065109</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E93" s="7">
         <v>0.47708247678697041</v>
@@ -5886,7 +6042,7 @@
         <v>1.479144949413123</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E94" s="5">
         <v>0.48410988604134297</v>
@@ -5903,7 +6059,7 @@
         <v>1.4422955263268871</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E95" s="7">
         <v>0.52658486382238012</v>
@@ -5920,7 +6076,7 @@
         <v>1.3819782779595431</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E96" s="5">
         <v>0.56458640004019844</v>
@@ -5937,7 +6093,7 @@
         <v>1.337114129613385</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E97" s="7">
         <v>0.59674322957248993</v>
@@ -5954,7 +6110,7 @@
         <v>1.2902859754489711</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E98" s="5">
         <v>0.62185524066953246</v>
@@ -5971,7 +6127,7 @@
         <v>1.2416282550221269</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E99" s="7">
         <v>0.6389644107562229</v>
@@ -5988,7 +6144,7 @@
         <v>1.191493961882963</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E100" s="5">
         <v>0.64741208149518248</v>
@@ -6005,7 +6161,7 @@
         <v>1.1403875614429311</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E101" s="7">
         <v>0.64687823497136121</v>
@@ -6022,7 +6178,7 @@
         <v>1.0888731942036181</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E102" s="5">
         <v>0.63739988589995256</v>
@@ -6039,7 +6195,7 @@
         <v>1.0375423869618841</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E103" s="7">
         <v>0.61936735871394311</v>
@@ -6056,7 +6212,7 @@
         <v>0.98687278826560287</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E104" s="5">
         <v>0.59349893032460632</v>
@@ -6073,7 +6229,7 @@
         <v>0.9381433599414607</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E105" s="7">
         <v>0.56079595655818371</v>
@@ -6090,7 +6246,7 @@
         <v>0.8161534208537049</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E106" s="5">
         <v>0.52248204342667925</v>
@@ -6107,7 +6263,7 @@
         <v>0.78995627967049897</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E107" s="7">
         <v>0.48692169707604588</v>
@@ -6124,7 +6280,7 @@
         <v>0.76246342090756258</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E108" s="5">
         <v>0.54098849359636425</v>
@@ -6141,7 +6297,7 @@
         <v>0.73345429580246613</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E109" s="7">
         <v>0.59426165618893456</v>
@@ -6158,7 +6314,7 @@
         <v>0.70262250162652284</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E110" s="5">
         <v>0.64578166656004243</v>
@@ -6175,7 +6331,7 @@
         <v>0.66944991785061758</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E111" s="7">
         <v>0.69468065713879157</v>
@@ -6192,7 +6348,7 @@
         <v>0.63353131434008814</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E112" s="5">
         <v>0.74022477434399059</v>
@@ -6209,7 +6365,7 @@
         <v>0.59532719514192634</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E113" s="7">
         <v>0.78184482739741723</v>
@@ -6226,7 +6382,7 @@
         <v>0.55561217221103076</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E114" s="5">
         <v>0.81915319146428844</v>
@@ -6243,7 +6399,7 @@
         <v>0.51537594551143184</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E115" s="7">
         <v>0.85194651300113178</v>
@@ -6260,7 +6416,7 @@
         <v>0.47572956368258679</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E116" s="5">
         <v>0.88019528099169109</v>
@@ -6277,7 +6433,7 @@
         <v>0.43784972277551698</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E117" s="7">
         <v>0.90402257646580997</v>
@@ -6294,7 +6450,7 @@
         <v>0.40271709267478611</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E118" s="5">
         <v>0.92367515034184844</v>
@@ -6311,7 +6467,7 @@
         <v>0.37122702244742772</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E119" s="7">
         <v>0.93949034053298364</v>
@@ -6328,7 +6484,7 @@
         <v>0</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E120" s="5">
         <v>0.95186223802182079</v>
@@ -6345,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E121" s="7">
         <v>0.96121003010736605</v>
@@ -6362,7 +6518,7 @@
         <v>0</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E122" s="5">
         <v>0.96795071292837365</v>
@@ -6379,7 +6535,7 @@
         <v>0</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E123" s="7">
         <v>0.97247751638465318</v>
@@ -6396,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E124" s="5">
         <v>0.97514455458892801</v>
@@ -6413,7 +6569,7 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E125" s="7">
         <v>0.9762575066684076</v>
@@ -6430,7 +6586,7 @@
         <v>0</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E126" s="5">
         <v>0.97606960923714603</v>
@@ -6447,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E127" s="7">
         <v>0.97478192554082976</v>
@@ -6464,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E128" s="5">
         <v>0.97254673482048604</v>
@@ -6481,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E129" s="7">
         <v>0.96947292242485361</v>
@@ -6498,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E130" s="5">
         <v>0.96563239804595236</v>
@@ -6515,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E131" s="7">
         <v>0.96106677621839243</v>
@@ -6532,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E132" s="5">
         <v>0.95579377657571563</v>
@@ -6549,7 +6705,7 @@
         <v>0</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E133" s="7">
         <v>0.94981300909036925</v>
@@ -6563,10 +6719,10 @@
         <v>0</v>
       </c>
       <c r="C134" s="5">
-        <v>0.37461354944035852</v>
+        <v>0.37550937617869617</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E134" s="5">
         <v>0.94311098186295395</v>
@@ -6580,10 +6736,10 @@
         <v>0</v>
       </c>
       <c r="C135" s="7">
-        <v>0.38877605830610112</v>
+        <v>0.38987518084131401</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E135" s="7">
         <v>0.93566529749026361</v>
@@ -6597,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="C136" s="5">
-        <v>0.40374484033837721</v>
+        <v>0.40506761469281299</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E136" s="5">
         <v>0.92744808886230123</v>
@@ -6614,10 +6770,10 @@
         <v>0</v>
       </c>
       <c r="C137" s="7">
-        <v>0.41948216639613212</v>
+        <v>0.4210622541492417</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E137" s="7">
         <v>0.91842879227563357</v>
@@ -6631,10 +6787,10 @@
         <v>0</v>
       </c>
       <c r="C138" s="5">
-        <v>0.43584693821148218</v>
+        <v>0.43774592083890618</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E138" s="5">
         <v>0.90857637361384835</v>
@@ -6648,10 +6804,10 @@
         <v>0</v>
       </c>
       <c r="C139" s="7">
-        <v>0.45280475114543489</v>
+        <v>0.45504098261051568</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E139" s="7">
         <v>0.89786112114450489</v>
@@ -6665,10 +6821,10 @@
         <v>0</v>
       </c>
       <c r="C140" s="5">
-        <v>0.47024999278999879</v>
+        <v>0.47286402769511482</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E140" s="5">
         <v>0.88625610434927637</v>
@@ -6682,10 +6838,10 @@
         <v>0</v>
       </c>
       <c r="C141" s="7">
-        <v>0.48807152467917969</v>
+        <v>0.4911049505036047</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E141" s="7">
         <v>0.87373837854999459</v>
@@ -6699,10 +6855,10 @@
         <v>0</v>
       </c>
       <c r="C142" s="5">
-        <v>0.50615592556526845</v>
+        <v>0.50965068141507031</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E142" s="5">
         <v>0.86028999442054377</v>
@@ -6716,10 +6872,10 @@
         <v>0</v>
       </c>
       <c r="C143" s="7">
-        <v>0.52438997255955078</v>
+        <v>0.52838757862561248</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E143" s="7">
         <v>0.84589885255879815</v>
@@ -6733,10 +6889,10 @@
         <v>0</v>
       </c>
       <c r="C144" s="5">
-        <v>0.54266298336556917</v>
+        <v>0.547203691043748</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E144" s="5">
         <v>0.83055942754643319</v>
@@ -6750,10 +6906,10 @@
         <v>0</v>
       </c>
       <c r="C145" s="7">
-        <v>0.56086893468483423</v>
+        <v>0.56599080761423404</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E145" s="7">
         <v>0.81427337380410258</v>
@@ -6767,10 +6923,10 @@
         <v>0</v>
       </c>
       <c r="C146" s="5">
-        <v>0.57893087536902088</v>
+        <v>0.58461708995378447</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E146" s="5">
         <v>0.79705001692250588</v>
@@ -6784,10 +6940,10 @@
         <v>0</v>
       </c>
       <c r="C147" s="7">
-        <v>0.59674359056464377</v>
+        <v>0.60300030507113722</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E147" s="7">
         <v>0.7789067285788025</v>
@@ -6801,10 +6957,10 @@
         <v>0</v>
       </c>
       <c r="C148" s="5">
-        <v>0.61415665938755271</v>
+        <v>0.62106318476850653</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E148" s="5">
         <v>0.75986918008483806</v>
@@ -6818,10 +6974,10 @@
         <v>0</v>
       </c>
       <c r="C149" s="7">
-        <v>0.63120293725350451</v>
+        <v>0.63867051474546888</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E149" s="7">
         <v>0.73997146851671103</v>
@@ -6835,10 +6991,10 @@
         <v>0</v>
       </c>
       <c r="C150" s="5">
-        <v>0.64776442542884716</v>
+        <v>0.65580360360669077</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E150" s="5">
         <v>0.71925610976500431</v>
@@ -6852,10 +7008,10 @@
         <v>0</v>
       </c>
       <c r="C151" s="7">
-        <v>0.66378714306956066</v>
+        <v>0.67234675465953286</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E151" s="7">
         <v>0.69777389432302228</v>
@@ -6869,10 +7025,10 @@
         <v>0</v>
       </c>
       <c r="C152" s="5">
-        <v>0.67928156738555279</v>
+        <v>0.68827736768124825</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E152" s="5">
         <v>0.6755836038752483</v>
@@ -6886,10 +7042,10 @@
         <v>0</v>
       </c>
       <c r="C153" s="7">
-        <v>0.69413382669829793</v>
+        <v>0.70359253135846678</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E153" s="7">
         <v>0.65275158950208723</v>
@@ -6903,10 +7059,10 @@
         <v>0</v>
       </c>
       <c r="C154" s="5">
-        <v>0.70848061524090689</v>
+        <v>0.71842666327760252</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E154" s="5">
         <v>0.62935121537001992</v>
@@ -6920,10 +7076,10 @@
         <v>0</v>
       </c>
       <c r="C155" s="7">
-        <v>0.72237218690308025</v>
+        <v>0.7328333814806316</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E155" s="7">
         <v>0.60546217495324672</v>
@@ -6937,10 +7093,10 @@
         <v>0</v>
       </c>
       <c r="C156" s="5">
-        <v>0.73589505992670001</v>
+        <v>0.74683377668589912</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E156" s="5">
         <v>0.58116968998315333</v>
@@ -6954,10 +7110,10 @@
         <v>0</v>
       </c>
       <c r="C157" s="7">
-        <v>0.74904929933345687</v>
+        <v>0.76045035779776249</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E157" s="7">
         <v>0.55656360531343085</v>
@@ -6971,10 +7127,10 @@
         <v>0</v>
       </c>
       <c r="C158" s="5">
-        <v>0.76188425230030332</v>
+        <v>0.77370612387913895</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E158" s="5">
         <v>0.53173739560507394</v>
@@ -6988,10 +7144,10 @@
         <v>0</v>
       </c>
       <c r="C159" s="7">
-        <v>0.87155140639993101</v>
+        <v>0.7866204816414567</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E159" s="7">
         <v>0.50678710207553723</v>
@@ -7005,13 +7161,13 @@
         <v>0</v>
       </c>
       <c r="C160" s="5">
-        <v>0.89494527454261086</v>
+        <v>0.79922082469592071</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E160" s="5">
-        <v>0.48181021943476859</v>
+        <v>0.51747722583378519</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7022,13 +7178,13 @@
         <v>0</v>
       </c>
       <c r="C161" s="7">
-        <v>0.91905397448782955</v>
+        <v>0.81152470114616815</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E161" s="7">
-        <v>0.47522581577582768</v>
+        <v>0.54219554000191572</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7039,13 +7195,13 @@
         <v>0</v>
       </c>
       <c r="C162" s="5">
-        <v>0.94384809375170697</v>
+        <v>0.82354957698038056</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E162" s="5">
-        <v>0.49069412474544782</v>
+        <v>0.56670131237252364</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7056,13 +7212,13 @@
         <v>0</v>
       </c>
       <c r="C163" s="7">
-        <v>0.96939301492127006</v>
+        <v>0.83531037690310184</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E163" s="7">
-        <v>0.50496746877153265</v>
+        <v>0.59089036348636625</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7073,13 +7229,13 @@
         <v>0</v>
       </c>
       <c r="C164" s="5">
-        <v>0.99568457628544871</v>
+        <v>0.84681914117252322</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E164" s="5">
-        <v>0.51791089589180062</v>
+        <v>0.61466000617681393</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7090,13 +7246,13 @@
         <v>0</v>
       </c>
       <c r="C165" s="7">
-        <v>1.0226969552587351</v>
+        <v>0.85807724148207698</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E165" s="7">
-        <v>0.52939865534809027</v>
+        <v>0.637909887524716</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7107,13 +7263,13 @@
         <v>0</v>
       </c>
       <c r="C166" s="5">
-        <v>1.0504064424387241</v>
+        <v>0.86910828370746696</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E166" s="5">
-        <v>0.53931616403311589</v>
+        <v>0.66054274519288991</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7124,13 +7280,13 @@
         <v>0</v>
       </c>
       <c r="C167" s="7">
-        <v>1.0785175485798</v>
+        <v>0.87975836267620633</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E167" s="7">
-        <v>0.5475618534486264</v>
+        <v>0.68246506443043387</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7141,13 +7297,13 @@
         <v>0</v>
       </c>
       <c r="C168" s="5">
-        <v>1.106680831058775</v>
+        <v>0.88983194061764215</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E168" s="5">
-        <v>0.55404885720476682</v>
+        <v>0.70358762545249653</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7158,13 +7314,13 @@
         <v>0</v>
       </c>
       <c r="C169" s="7">
-        <v>1.134736841394816</v>
+        <v>0.89929954282430191</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E169" s="7">
-        <v>0.55870650119124621</v>
+        <v>0.72382593469563095</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7175,13 +7331,13 @@
         <v>0</v>
       </c>
       <c r="C170" s="5">
-        <v>1.162622884516566</v>
+        <v>0.90818860614317398</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E170" s="5">
-        <v>0.56148156169009011</v>
+        <v>0.7431005374959293</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7192,13 +7348,13 @@
         <v>0</v>
       </c>
       <c r="C171" s="7">
-        <v>1.190222124802788</v>
+        <v>0.9164962762930815</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E171" s="7">
-        <v>0.56233926083776065</v>
+        <v>0.76133721389761355</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7209,13 +7365,13 @@
         <v>0</v>
       </c>
       <c r="C172" s="5">
-        <v>1.2174214322961221</v>
+        <v>0.92424780208559931</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E172" s="5">
-        <v>0.5612639739086569</v>
+        <v>0.77846706342626781</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7226,13 +7382,13 @@
         <v>0</v>
       </c>
       <c r="C173" s="7">
-        <v>1.244134357188023</v>
+        <v>0.9314377331979653</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E173" s="7">
-        <v>0.55825962877708635</v>
+        <v>0.79442648860300202</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7243,13 +7399,13 @@
         <v>0</v>
       </c>
       <c r="C174" s="5">
-        <v>1.270314030105379</v>
+        <v>0.93810758680894157</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E174" s="5">
-        <v>0.55334978448411043</v>
+        <v>0.809157090585226</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7260,13 +7416,13 @@
         <v>0</v>
       </c>
       <c r="C175" s="7">
-        <v>1.295860447804897</v>
+        <v>0.94427258101504064</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E175" s="7">
-        <v>0.54657738292419689</v>
+        <v>0.82260549345563305</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7277,13 +7433,13 @@
         <v>0</v>
       </c>
       <c r="C176" s="5">
-        <v>1.3207709674256449</v>
+        <v>0.94995087275901102</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E176" s="5">
-        <v>0.53800417508522191</v>
+        <v>0.83472311621549633</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7294,13 +7450,13 @@
         <v>0</v>
       </c>
       <c r="C177" s="7">
-        <v>1.3449800057164309</v>
+        <v>0.955163328398277</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E177" s="7">
-        <v>0.52770983081627565</v>
+        <v>0.84546591336140975</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7311,13 +7467,13 @@
         <v>0</v>
       </c>
       <c r="C178" s="5">
-        <v>1.368457913662585</v>
+        <v>0.95993326470630125</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E178" s="5">
-        <v>0.51579074854116513</v>
+        <v>0.85479410594856353</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7328,13 +7484,13 @@
         <v>0</v>
       </c>
       <c r="C179" s="7">
-        <v>1.3912058371150791</v>
+        <v>0.96428244693910836</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E179" s="7">
-        <v>0.50235858845727366</v>
+        <v>0.86267192520748548</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7345,13 +7501,13 @@
         <v>0</v>
       </c>
       <c r="C180" s="5">
-        <v>1.413193815687636</v>
+        <v>0.96824028939746531</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E180" s="5">
-        <v>0.4875385593390843</v>
+        <v>0.86906739005366718</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7362,13 +7518,13 @@
         <v>0</v>
       </c>
       <c r="C181" s="7">
-        <v>1.4345603768122721</v>
+        <v>0.97183295305079587</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E181" s="7">
-        <v>0.47146749489497519</v>
+        <v>0.87395213821161044</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7379,13 +7535,13 @@
         <v>0</v>
       </c>
       <c r="C182" s="5">
-        <v>1.4553526809018089</v>
+        <v>0.97509181234046538</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E182" s="5">
-        <v>0.45429176051718478</v>
+        <v>0.87730132820116502</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7396,13 +7552,13 @@
         <v>0</v>
       </c>
       <c r="C183" s="7">
-        <v>1.4960941671083019</v>
+        <v>1.058059617962434</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E183" s="7">
-        <v>0.44292859111407851</v>
+        <v>0.87909362617295872</v>
       </c>
     </row>
     <row r="184" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7413,13 +7569,13 @@
         <v>0</v>
       </c>
       <c r="C184" s="5">
-        <v>1.5189216284835301</v>
+        <v>1.07166001026751</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E184" s="5">
-        <v>0.46206527278738779</v>
+        <v>0.87931128763246669</v>
       </c>
     </row>
     <row r="185" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7430,13 +7586,13 @@
         <v>0</v>
       </c>
       <c r="C185" s="7">
-        <v>1.5418396554542459</v>
+        <v>1.086054264077934</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E185" s="7">
-        <v>0.48024425119774161</v>
+        <v>0.87794033959047546</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7447,13 +7603,13 @@
         <v>0</v>
       </c>
       <c r="C186" s="5">
-        <v>1.5841284648973659</v>
+        <v>1.116854298525717</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E186" s="5">
-        <v>0.49729383353856971</v>
+        <v>0.87497086377999467</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7464,13 +7620,13 @@
         <v>0</v>
       </c>
       <c r="C187" s="7">
-        <v>1.6053969597044351</v>
+        <v>1.130851877276541</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E187" s="7">
-        <v>0.51304861557799675</v>
+        <v>0.87039737646658932</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7481,13 +7637,13 @@
         <v>0</v>
       </c>
       <c r="C188" s="5">
-        <v>1.627334207361911</v>
+        <v>1.145868108686654</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E188" s="5">
-        <v>0.5273520781092893</v>
+        <v>0.86421929524720309</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7498,13 +7654,13 @@
         <v>0</v>
       </c>
       <c r="C189" s="7">
-        <v>1.6499741347453389</v>
+        <v>1.161879861127753</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E189" s="7">
-        <v>0.54005910498012188</v>
+        <v>0.85644147828719308</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7515,13 +7671,13 @@
         <v>0</v>
       </c>
       <c r="C190" s="5">
-        <v>1.673308431398743</v>
+        <v>1.1788553233539181</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E190" s="5">
-        <v>0.55103836804933604</v>
+        <v>0.84707481689289965</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7532,13 +7688,13 @@
         <v>0</v>
       </c>
       <c r="C191" s="7">
-        <v>1.697356820352663</v>
+        <v>1.1967545711694461</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E191" s="7">
-        <v>0.56017452621534236</v>
+        <v>0.83613685835656226</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7549,13 +7705,13 @@
         <v>0</v>
       </c>
       <c r="C192" s="5">
-        <v>1.722071546890134</v>
+        <v>1.2155433476478521</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E192" s="5">
-        <v>0.56737018888451085</v>
+        <v>0.82365243282472722</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7566,13 +7722,13 @@
         <v>0</v>
       </c>
       <c r="C193" s="7">
-        <v>1.7474713278174301</v>
+        <v>1.235185190420597</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E193" s="7">
-        <v>0.57254759883572026</v>
+        <v>0.80965425568894922</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7583,13 +7739,13 @@
         <v>0</v>
       </c>
       <c r="C194" s="5">
-        <v>1.773526249209789</v>
+        <v>1.255584526445513</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E194" s="5">
-        <v>0.57564999528170524</v>
+        <v>0.7941834758048385</v>
       </c>
     </row>
     <row r="195" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7600,13 +7756,13 @@
         <v>0</v>
       </c>
       <c r="C195" s="7">
-        <v>1.8001327659181521</v>
+        <v>1.276744407361541</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E195" s="7">
-        <v>0.5766426248828358</v>
+        <v>0.77729013979951089</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7617,13 +7773,13 @@
         <v>0</v>
       </c>
       <c r="C196" s="5">
-        <v>1.827286100962678</v>
+        <v>1.298592764232821</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E196" s="5">
-        <v>0.57551337635328181</v>
+        <v>0.75903354387096633</v>
       </c>
     </row>
     <row r="197" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7634,13 +7790,13 @@
         <v>0</v>
       </c>
       <c r="C197" s="7">
-        <v>1.8548680469335579</v>
+        <v>1.321120825824833</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E197" s="7">
-        <v>0.57227302290200655</v>
+        <v>0.73948244681040509</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7651,13 +7807,13 @@
         <v>0</v>
       </c>
       <c r="C198" s="5">
-        <v>1.8828003683529639</v>
+        <v>1.3442370389688409</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E198" s="5">
-        <v>0.56695506583660116</v>
+        <v>0.71871512143483296</v>
       </c>
     </row>
     <row r="199" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7668,13 +7824,13 @@
         <v>0</v>
       </c>
       <c r="C199" s="7">
-        <v>1.9109856217628081</v>
+        <v>1.3679788448099071</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E199" s="7">
-        <v>0.55961518197453652</v>
+        <v>0.69681922609819158</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7685,13 +7841,13 @@
         <v>0</v>
       </c>
       <c r="C200" s="5">
-        <v>1.939324612431566</v>
+        <v>1.3923026242580661</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E200" s="5">
-        <v>0.55033028679235585</v>
+        <v>0.67389148330433402</v>
       </c>
     </row>
     <row r="201" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7702,13 +7858,13 @@
         <v>0</v>
       </c>
       <c r="C201" s="7">
-        <v>1.9676645271059141</v>
+        <v>1.417174140665806</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E201" s="7">
-        <v>0.53919723423548049</v>
+        <v>0.65003715848314347</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7719,13 +7875,13 @@
         <v>0</v>
       </c>
       <c r="C202" s="5">
-        <v>1.9954784246924719</v>
+        <v>1.442609669037789</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E202" s="5">
-        <v>0.52633118255317723</v>
+        <v>0.62536933848739729</v>
       </c>
     </row>
     <row r="203" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7736,13 +7892,13 @@
         <v>0</v>
       </c>
       <c r="C203" s="7">
-        <v>2.0226361731849791</v>
+        <v>1.4686295060877459</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E203" s="7">
-        <v>0.51186366317310439</v>
+        <v>0.60000801607372845</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7753,13 +7909,13 @@
         <v>0</v>
       </c>
       <c r="C204" s="5">
-        <v>2.049107799084652</v>
+        <v>1.4952625563784829</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E204" s="5">
-        <v>0.49594039626883268</v>
+        <v>0.57407899328406409</v>
       </c>
     </row>
     <row r="205" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7770,13 +7926,13 @@
         <v>0</v>
       </c>
       <c r="C205" s="7">
-        <v>2.0749134813627719</v>
+        <v>1.5225254738363081</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E205" s="7">
-        <v>0.47871890211300211</v>
+        <v>0.54771262298009704</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7787,13 +7943,13 @@
         <v>0</v>
       </c>
       <c r="C206" s="5">
-        <v>2.1000723216133879</v>
+        <v>1.550455839064147</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E206" s="5">
-        <v>0.47724266731684378</v>
+        <v>0.52104241354879555</v>
       </c>
     </row>
     <row r="207" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -7804,10 +7960,10 @@
         <v>0</v>
       </c>
       <c r="C207" s="7">
-        <v>2.12457755442506</v>
+        <v>1.57909770356914</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E207" s="7">
         <v>0.50439681644012635</v>
@@ -7821,10 +7977,10 @@
         <v>0</v>
       </c>
       <c r="C208" s="5">
-        <v>2.2386759094826671</v>
+        <v>1.608500070998176</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E208" s="5">
         <v>0.53153060134890495</v>
@@ -7838,10 +7994,10 @@
         <v>0</v>
       </c>
       <c r="C209" s="7">
-        <v>2.252789849626184</v>
+        <v>1.638715109014673</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E209" s="7">
         <v>0.55851864791386685</v>
@@ -7855,10 +8011,10 @@
         <v>0</v>
       </c>
       <c r="C210" s="5">
-        <v>2.2673025162724851</v>
+        <v>1.669796021618202</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E210" s="5">
         <v>0.58523759975245371</v>
@@ -7872,10 +8028,10 @@
         <v>0</v>
       </c>
       <c r="C211" s="7">
-        <v>2.2822106349264568</v>
+        <v>1.701794497912998</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E211" s="7">
         <v>0.61156780696885371</v>
@@ -7889,10 +8045,10 @@
         <v>0</v>
       </c>
       <c r="C212" s="5">
-        <v>2.2975737547002808</v>
+        <v>1.734757643162163</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E212" s="5">
         <v>0.63739492993797531</v>
@@ -7906,10 +8062,10 @@
         <v>0</v>
       </c>
       <c r="C213" s="7">
-        <v>2.3135017376066469</v>
+        <v>1.7687242938594829</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E213" s="7">
         <v>0.66261142238711779</v>
@@ -7923,10 +8079,10 @@
         <v>0</v>
       </c>
       <c r="C214" s="5">
-        <v>2.3300766012183161</v>
+        <v>1.803720624102229</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E214" s="5">
         <v>0.68711786186383483</v>
@@ -7940,10 +8096,10 @@
         <v>0</v>
       </c>
       <c r="C215" s="7">
-        <v>2.347354731030785</v>
+        <v>1.839754970692089</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E215" s="7">
         <v>0.71082410046970679</v>
@@ -7957,10 +8113,10 @@
         <v>0</v>
       </c>
       <c r="C216" s="5">
-        <v>2.3652095984884389</v>
+        <v>1.876811845426382</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E216" s="5">
         <v>0.73365021429435073</v>
@@ -7974,10 +8130,10 @@
         <v>0</v>
       </c>
       <c r="C217" s="7">
-        <v>2.3836472962838129</v>
+        <v>1.914902111416281</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E217" s="7">
         <v>0.75552723608180572</v>
@@ -7991,10 +8147,10 @@
         <v>0</v>
       </c>
       <c r="C218" s="5">
-        <v>2.4025331161098249</v>
+        <v>1.9539269046416541</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E218" s="5">
         <v>0.77639766206569849</v>
@@ -8008,10 +8164,10 @@
         <v>0</v>
       </c>
       <c r="C219" s="7">
-        <v>2.421850761520608</v>
+        <v>1.993821269658403</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E219" s="7">
         <v>0.79621573037827176</v>
@@ -8025,10 +8181,10 @@
         <v>0</v>
       </c>
       <c r="C220" s="5">
-        <v>2.441445956587736</v>
+        <v>2.0344507689899989</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E220" s="5">
         <v>0.81494747473519369</v>
@@ -8042,10 +8198,10 @@
         <v>0</v>
       </c>
       <c r="C221" s="7">
-        <v>2.4611838586653931</v>
+        <v>2.075707721231951</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E221" s="7">
         <v>0.83257056300304644</v>
@@ -8059,10 +8215,10 @@
         <v>0</v>
       </c>
       <c r="C222" s="5">
-        <v>2.4809738587696768</v>
+        <v>2.1173546301191499</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E222" s="5">
         <v>0.84907393557496924</v>
@@ -8076,10 +8232,10 @@
         <v>0</v>
       </c>
       <c r="C223" s="7">
-        <v>2.5006984903712381</v>
+        <v>2.1591892185370729</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E223" s="7">
         <v>0.86445726305063175</v>
@@ -8093,10 +8249,10 @@
         <v>3</v>
       </c>
       <c r="C224" s="5">
-        <v>2.520181761993511</v>
+        <v>2.2009810746502692</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E224" s="5">
         <v>0.87873024641664466</v>
@@ -8110,10 +8266,10 @@
         <v>3</v>
       </c>
       <c r="C225" s="7">
-        <v>2.53928261604469</v>
+        <v>2.2424739205660802</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E225" s="7">
         <v>0.89191178567183238</v>
@@ -8127,10 +8283,10 @@
         <v>3</v>
       </c>
       <c r="C226" s="5">
-        <v>2.5578755409599401</v>
+        <v>2.283389376320895</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E226" s="5">
         <v>0.90402904460076206</v>
@@ -8144,10 +8300,10 @@
         <v>3</v>
       </c>
       <c r="C227" s="7">
-        <v>2.5758562769460278</v>
+        <v>2.3234322599486839</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E227" s="7">
         <v>0.91511644017290805</v>
@@ -8161,10 +8317,10 @@
         <v>3</v>
       </c>
       <c r="C228" s="5">
-        <v>2.593078746838327</v>
+        <v>2.362297344670242</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E228" s="5">
         <v>0.92521458487723884</v>
@@ -8178,10 +8334,10 @@
         <v>3</v>
       </c>
       <c r="C229" s="7">
-        <v>2.6094302009407571</v>
+        <v>2.399677357271278</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E229" s="7">
         <v>0.93436920927056877</v>
@@ -8195,10 +8351,10 @@
         <v>3</v>
       </c>
       <c r="C230" s="5">
-        <v>2.624855480161302</v>
+        <v>2.4354765195859742</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E230" s="5">
         <v>0.94263009022871236</v>
@@ -8215,7 +8371,7 @@
         <v>2.752583064698948</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E231" s="7">
         <v>0.95005000796960881</v>
@@ -8232,7 +8388,7 @@
         <v>2.7527457581579058</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E232" s="5">
         <v>0.95668375200838762</v>
@@ -8249,7 +8405,7 @@
         <v>2.7528755395622211</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E233" s="7">
         <v>0.96258719295348438</v>
@@ -8266,7 +8422,7 @@
         <v>2.752973578688191</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E234" s="5">
         <v>0.96781643360751035</v>
@@ -8283,7 +8439,7 @@
         <v>2.753059952452062</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E235" s="7">
         <v>0.97242704933672519</v>
@@ -8300,7 +8456,7 @@
         <v>2.753116940716358</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E236" s="5">
         <v>0.97647342424643202</v>
@@ -8317,7 +8473,7 @@
         <v>2.7531619722505298</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E237" s="7">
         <v>0.98000818645751664</v>
@@ -8334,7 +8490,7 @@
         <v>2.7532011145704391</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E238" s="5">
         <v>0.9830817428131956</v>
@@ -8351,7 +8507,7 @@
         <v>2.7532349820830029</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E239" s="7">
         <v>0.98574191072496864</v>
@@ -8368,7 +8524,7 @@
         <v>2.753255632510236</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E240" s="5">
         <v>0.98803364264106242</v>
@@ -8385,7 +8541,7 @@
         <v>2.7532683964114888</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E241" s="7">
         <v>0.98999883681629841</v>
@@ -8402,7 +8558,7 @@
         <v>2.7532792899843348</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E242" s="5">
         <v>0.99167622668654765</v>
@@ -8419,7 +8575,7 @@
         <v>2.753288544428008</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E243" s="7">
         <v>0.99310134019348117</v>
@@ -8436,7 +8592,7 @@
         <v>2.7532963701169679</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E244" s="5">
         <v>0.99430651984118001</v>
@@ -8453,7 +8609,7 @@
         <v>2.7533029570983478</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E245" s="7">
         <v>0.99532099405873042</v>
@@ -8470,7 +8626,7 @@
         <v>2.753308475854968</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E246" s="5">
         <v>0.99617099054718361</v>
@@ -8487,7 +8643,7 @@
         <v>2.7533130782769311</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E247" s="7">
         <v>0.99687988265488581</v>
@@ -8504,7 +8660,7 @@
         <v>2.753316898788392</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E248" s="5">
         <v>0.9974683603996064</v>
@@ -8521,7 +8677,7 @@
         <v>2.7533200555807542</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E249" s="7">
         <v>0.99795461848665556</v>
@@ -8538,7 +8694,7 @@
         <v>2.7533226519088578</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E250" s="5">
         <v>0.99835455450939836</v>
@@ -8555,7 +8711,7 @@
         <v>2.7533247774124319</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E251" s="7">
         <v>0.99868197141633519</v>
@@ -8572,7 +8728,7 @@
         <v>2.7533265094308979</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E252" s="5">
         <v>0.99894877924685821</v>
@@ -8589,7 +8745,7 @@
         <v>2.753327914285431</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E253" s="7">
         <v>0.99916519204154042</v>
@@ -8606,7 +8762,7 @@
         <v>2.7533290485076241</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E254" s="5">
         <v>0.99933991669471123</v>
@@ -8620,7 +8776,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E154"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8633,8 +8789,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>15</v>
+      <c r="A1" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -8643,19 +8799,19 @@
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -8669,7 +8825,7 @@
         <v>2.7533333324762199</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E4" s="5">
         <v>0.99999986795826801</v>
@@ -8686,7 +8842,7 @@
         <v>2.7533333315517452</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E5" s="7">
         <v>0.99999972553918881</v>
@@ -8703,7 +8859,7 @@
         <v>2.753333329698767</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E6" s="5">
         <v>0.99999944008027164</v>
@@ -8720,7 +8876,7 @@
         <v>2.753333326055746</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E7" s="7">
         <v>0.99999887885827843</v>
@@ -8737,7 +8893,7 @@
         <v>2.753333319030391</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E8" s="5">
         <v>0.99999779657388999</v>
@@ -8754,7 +8910,7 @@
         <v>2.7533333057414402</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E9" s="7">
         <v>0.99999574935742019</v>
@@ -8771,7 +8927,7 @@
         <v>2.7533332810850868</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E10" s="5">
         <v>0.99999195094762983</v>
@@ -8788,7 +8944,7 @@
         <v>2.7533332362123368</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E11" s="7">
         <v>0.99998503812268602</v>
@@ -8805,7 +8961,7 @@
         <v>2.7533331561086771</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E12" s="5">
         <v>0.99997269784280585</v>
@@ -8822,7 +8978,7 @@
         <v>2.7533330158473559</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E13" s="7">
         <v>0.99995109006114336</v>
@@ -8839,7 +8995,7 @@
         <v>2.7533327749458572</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E14" s="5">
         <v>0.99991397834028162</v>
@@ -8856,7 +9012,7 @@
         <v>2.753332369103564</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E15" s="7">
         <v>0.99985145707567402</v>
@@ -8873,7 +9029,7 @@
         <v>2.753331698460213</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E16" s="5">
         <v>0.99974814283719959</v>
@@ -8890,7 +9046,7 @@
         <v>2.7533306114267329</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E17" s="7">
         <v>0.99958068388058441</v>
@@ -8907,7 +9063,7 @@
         <v>2.753328883155632</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E18" s="5">
         <v>0.99931444445206719</v>
@@ -8924,7 +9080,7 @@
         <v>2.7533261879031832</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E19" s="7">
         <v>0.99889924940393438</v>
@@ -8941,7 +9097,7 @@
         <v>2.753322064962763</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E20" s="5">
         <v>0.99826414112967365</v>
@@ -8958,7 +9114,7 @@
         <v>2.7533158785821179</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E21" s="7">
         <v>0.9973112150779132</v>
@@ -8975,7 +9131,7 @@
         <v>2.753306773354161</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E22" s="5">
         <v>0.99590876805870998</v>
@@ -8992,7 +9148,7 @@
         <v>2.7532936279754612</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E23" s="7">
         <v>0.99388421309605302</v>
@@ -9009,7 +9165,7 @@
         <v>2.7532750119066831</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E24" s="5">
         <v>0.99101747159932085</v>
@@ -9026,7 +9182,7 @@
         <v>2.7532491511583692</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E25" s="7">
         <v>0.98703581907143201</v>
@@ -9043,7 +9199,7 @@
         <v>2.7531823909281918</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E26" s="5">
         <v>0.98161138977753437</v>
@@ -9060,7 +9216,7 @@
         <v>2.7530900426527669</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E27" s="7">
         <v>0.9743626814108336</v>
@@ -9077,7 +9233,7 @@
         <v>2.7529181865627921</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E28" s="5">
         <v>0.96486138014403244</v>
@@ -9094,7 +9250,7 @@
         <v>2.7526467489140169</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E29" s="7">
         <v>0.95264559334921117</v>
@@ -9111,7 +9267,7 @@
         <v>2.613235222692126</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E30" s="5">
         <v>0.93724009683638243</v>
@@ -9128,7 +9284,7 @@
         <v>2.5789505862824318</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E31" s="7">
         <v>0.91818347735394457</v>
@@ -9145,7 +9301,7 @@
         <v>2.5413500934672482</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E32" s="5">
         <v>0.89506112918755665</v>
@@ -9162,7 +9318,7 @@
         <v>2.50145480805097</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E33" s="7">
         <v>0.86754204812857383</v>
@@ -9179,7 +9335,7 @@
         <v>2.460487944564496</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E34" s="5">
         <v>0.83541640429508379</v>
@@ -9196,7 +9352,7 @@
         <v>2.4196995649126212</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E35" s="7">
         <v>0.79863014070265059</v>
@@ -9213,7 +9369,7 @@
         <v>2.380225326952492</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E36" s="5">
         <v>0.75731250654703852</v>
@@ -9230,7 +9386,7 @@
         <v>2.34296002775329</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E37" s="7">
         <v>0.71179262266979704</v>
@@ -9247,7 +9403,7 @@
         <v>2.3085813059917348</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E38" s="5">
         <v>0.66260194792509042</v>
@@ -9264,7 +9420,7 @@
         <v>2.2769924513797482</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E39" s="7">
         <v>0.61046082850660177</v>
@@ -9281,7 +9437,7 @@
         <v>2.247477156449242</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E40" s="5">
         <v>0.55624902443269131</v>
@@ -9298,7 +9454,7 @@
         <v>2.219697590788861</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E41" s="7">
         <v>0.50096198829580552</v>
@@ -9315,7 +9471,7 @@
         <v>2.087509253071159</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E42" s="5">
         <v>0.49495280808760239</v>
@@ -9332,7 +9488,7 @@
         <v>2.0286223294268928</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E43" s="7">
         <v>0.52616053634885729</v>
@@ -9349,7 +9505,7 @@
         <v>1.964243847534918</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E44" s="5">
         <v>0.54916140878343156</v>
@@ -9366,7 +9522,7 @@
         <v>1.895865540264204</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E45" s="7">
         <v>0.5624869759978961</v>
@@ -9383,7 +9539,7 @@
         <v>1.8263752266136231</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E46" s="5">
         <v>0.56512575807772203</v>
@@ -9400,7 +9556,7 @@
         <v>1.757519377142057</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E47" s="7">
         <v>0.55664352797510297</v>
@@ -9417,7 +9573,7 @@
         <v>1.691001599785839</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E48" s="5">
         <v>0.53725640559257581</v>
@@ -9434,7 +9590,7 @@
         <v>1.6281344704525429</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E49" s="7">
         <v>0.50784219416635079</v>
@@ -9451,7 +9607,7 @@
         <v>1.5698558618005269</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E50" s="5">
         <v>0.46988317749411729</v>
@@ -9468,7 +9624,7 @@
         <v>1.5156236971085491</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E51" s="7">
         <v>0.46588812651158579</v>
@@ -9485,7 +9641,7 @@
         <v>1.464315908061679</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E52" s="5">
         <v>0.51806363888703111</v>
@@ -9502,7 +9658,7 @@
         <v>1.3702925379963911</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E53" s="7">
         <v>0.56150193617614852</v>
@@ -9519,7 +9675,7 @@
         <v>1.313843239204064</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E54" s="5">
         <v>0.59274630197761025</v>
@@ -9536,7 +9692,7 @@
         <v>1.252700447216867</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E55" s="7">
         <v>0.60892016622439504</v>
@@ -9553,7 +9709,7 @@
         <v>1.186478123336947</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E56" s="5">
         <v>0.6081386526392174</v>
@@ -9570,7 +9726,7 @@
         <v>1.1154802111766331</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E57" s="7">
         <v>0.58984476302121602</v>
@@ -9587,7 +9743,7 @@
         <v>1.040523097836763</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E58" s="5">
         <v>0.5549922355351834</v>
@@ -9604,7 +9760,7 @@
         <v>0.96516421057227975</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E59" s="7">
         <v>0.50601544757281958</v>
@@ -9621,7 +9777,7 @@
         <v>0.89314965496869247</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E60" s="5">
         <v>0.48922075288222089</v>
@@ -9638,7 +9794,7 @@
         <v>0.73651421105871884</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E61" s="7">
         <v>0.57357175715517605</v>
@@ -9655,7 +9811,7 @@
         <v>0.68783739285178025</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E62" s="5">
         <v>0.65467487567159977</v>
@@ -9672,7 +9828,7 @@
         <v>0.63351747511126077</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E63" s="7">
         <v>0.72922479689802255</v>
@@ -9689,7 +9845,7 @@
         <v>0.574312850558653</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E64" s="5">
         <v>0.79473617475268299</v>
@@ -9706,7 +9862,7 @@
         <v>0.51291240701331875</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E65" s="7">
         <v>0.84977066260249812</v>
@@ -9723,7 +9879,7 @@
         <v>0.45298857381847091</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E66" s="5">
         <v>0.893963466390991</v>
@@ -9740,7 +9896,7 @@
         <v>0.39848924160796012</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E67" s="7">
         <v>0.92786752174244924</v>
@@ -9757,7 +9913,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E68" s="5">
         <v>0.95266752046513981</v>
@@ -9774,7 +9930,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E69" s="7">
         <v>0.96982440280181681</v>
@@ -9791,7 +9947,7 @@
         <v>0</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E70" s="5">
         <v>0.98069521990306519</v>
@@ -9808,7 +9964,7 @@
         <v>0</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E71" s="7">
         <v>0.98614849278859462</v>
@@ -9825,7 +9981,7 @@
         <v>0</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E72" s="5">
         <v>0.98618652674439922</v>
@@ -9842,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E73" s="7">
         <v>0.97961791850684621</v>
@@ -9859,7 +10015,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E74" s="5">
         <v>0.96389836643779481</v>
@@ -9876,7 +10032,7 @@
         <v>0.36925272814528409</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E75" s="7">
         <v>0.93533418221427678</v>
@@ -9893,7 +10049,7 @@
         <v>0.44189175584810431</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E76" s="5">
         <v>0.88983474279902208</v>
@@ -9910,7 +10066,7 @@
         <v>0.52632529319562782</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E77" s="7">
         <v>0.82422695501444299</v>
@@ -9927,7 +10083,7 @@
         <v>0.61246951095158519</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E78" s="5">
         <v>0.73782026468433082</v>
@@ -9944,7 +10100,7 @@
         <v>0.81190041175988503</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E79" s="7">
         <v>0.63359929317112063</v>
@@ -9961,7 +10117,7 @@
         <v>0.90578215646777582</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E80" s="5">
         <v>0.51837269395543584</v>
@@ -9978,7 +10134,7 @@
         <v>0.99939664192115862</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E81" s="7">
         <v>0.49198231099471768</v>
@@ -9995,7 +10151,7 @@
         <v>1.0938974865027269</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E82" s="5">
         <v>0.56444314215517233</v>
@@ -10012,7 +10168,7 @@
         <v>1.1802922710768</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E83" s="7">
         <v>0.6133852496150094</v>
@@ -10029,7 +10185,7 @@
         <v>1.2561533785844241</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E84" s="5">
         <v>0.63469127066858211</v>
@@ -10046,7 +10202,7 @@
         <v>1.322700448594055</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E85" s="7">
         <v>0.62864911970214987</v>
@@ -10063,7 +10219,7 @@
         <v>1.3966551325843839</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E86" s="5">
         <v>0.59907012539149807</v>
@@ -10080,7 +10236,7 @@
         <v>1.44335593611346</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E87" s="7">
         <v>0.55175845345044738</v>
@@ -10097,7 +10253,7 @@
         <v>1.490442589394541</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E88" s="5">
         <v>0.4930081836080647</v>
@@ -10114,7 +10270,7 @@
         <v>1.5384783491865619</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E89" s="7">
         <v>0.52724499197532737</v>
@@ -10131,7 +10287,7 @@
         <v>1.6071329374222481</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E90" s="5">
         <v>0.58091958258332665</v>
@@ -10148,7 +10304,7 @@
         <v>1.6649874376427189</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E91" s="7">
         <v>0.62667624602500849</v>
@@ -10165,7 +10321,7 @@
         <v>1.725158481750056</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E92" s="5">
         <v>0.6623628993528724</v>
@@ -10182,7 +10338,7 @@
         <v>1.786564813487084</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E93" s="7">
         <v>0.68638683977377957</v>
@@ -10199,7 +10355,7 @@
         <v>1.8477972523448869</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E94" s="5">
         <v>0.69781844672174143</v>
@@ -10216,7 +10372,7 @@
         <v>1.90750815230246</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E95" s="7">
         <v>0.69642667874857733</v>
@@ -10233,7 +10389,7 @@
         <v>1.964522364968561</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E96" s="5">
         <v>0.68265053247306162</v>
@@ -10250,7 +10406,7 @@
         <v>2.0182938137095539</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E97" s="7">
         <v>0.65751848236034172</v>
@@ -10267,7 +10423,7 @@
         <v>2.1349560906003151</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E98" s="5">
         <v>0.62253205189363403</v>
@@ -10284,7 +10440,7 @@
         <v>2.1612857217093548</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E99" s="7">
         <v>0.57953016745610308</v>
@@ -10301,7 +10457,7 @@
         <v>2.1889071416814558</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E100" s="5">
         <v>0.53054879778797193</v>
@@ -10318,7 +10474,7 @@
         <v>2.2180219750708541</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E101" s="7">
         <v>0.511302242947129</v>
@@ -10335,7 +10491,7 @@
         <v>2.2489400785376108</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E102" s="5">
         <v>0.57019663327357051</v>
@@ -10352,7 +10508,7 @@
         <v>2.281984980338168</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E103" s="7">
         <v>0.62756660629923233</v>
@@ -10369,7 +10525,7 @@
         <v>2.317542814937243</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E104" s="5">
         <v>0.68223427733623587</v>
@@ -10386,7 +10542,7 @@
         <v>2.3564544860120278</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E105" s="7">
         <v>0.73319219920201828</v>
@@ -10403,7 +10559,7 @@
         <v>2.3983437922930588</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E106" s="5">
         <v>0.7796574249502497</v>
@@ -10420,7 +10576,7 @@
         <v>2.442152534544388</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E107" s="7">
         <v>0.82110313625731635</v>
@@ -10437,7 +10593,7 @@
         <v>2.486567150778872</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E108" s="5">
         <v>0.85726629371726815</v>
@@ -10454,7 +10610,7 @@
         <v>2.5300974711289599</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E109" s="7">
         <v>0.88813285723132729</v>
@@ -10471,7 +10627,7 @@
         <v>2.5712444995950041</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E110" s="5">
         <v>0.91390469602570579</v>
@@ -10488,7 +10644,7 @@
         <v>2.6086858024061459</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E111" s="7">
         <v>0.93495399864822959</v>
@@ -10505,7 +10661,7 @@
         <v>2.7526253099501869</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E112" s="5">
         <v>0.95177164401240544</v>
@@ -10522,7 +10678,7 @@
         <v>2.7529192041258121</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E113" s="7">
         <v>0.96491565254211276</v>
@@ -10539,7 +10695,7 @@
         <v>2.7530977152485372</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E114" s="5">
         <v>0.97496471692131403</v>
@@ -10556,7 +10712,7 @@
         <v>2.7531934551739559</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E115" s="7">
         <v>0.98248022885380359</v>
@@ -10573,7 +10729,7 @@
         <v>2.7532552743808658</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E116" s="5">
         <v>0.98797850618162175</v>
@@ -10590,7 +10746,7 @@
         <v>2.753280830008209</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E117" s="7">
         <v>0.99191337116303402</v>
@@ -10607,7 +10763,7 @@
         <v>2.753298717455908</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E118" s="5">
         <v>0.99466803200773624</v>
@@ -10624,7 +10780,7 @@
         <v>2.7533109655558579</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E119" s="7">
         <v>0.9965544656415084</v>
@@ -10641,7 +10797,7 @@
         <v>2.753319169849394</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E120" s="5">
         <v>0.99781818315848825</v>
@@ -10658,7 +10814,7 @@
         <v>2.7533245458687059</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E121" s="7">
         <v>0.99864630367449836</v>
@@ -10675,7 +10831,7 @@
         <v>2.7533279919369562</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E122" s="5">
         <v>0.9991771540519796</v>
@@ -10692,7 +10848,7 @@
         <v>2.753330152801881</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E123" s="7">
         <v>0.99951003255353499</v>
@@ -10709,7 +10865,7 @@
         <v>2.7533314782725218</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E124" s="5">
         <v>0.99971422251076281</v>
@@ -10726,7 +10882,7 @@
         <v>2.753332273607354</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E125" s="7">
         <v>0.99983674561820757</v>
@@ -10743,7 +10899,7 @@
         <v>2.7533327404455492</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E126" s="5">
         <v>0.99990866345280638</v>
@@ -10760,7 +10916,7 @@
         <v>2.7533330084972958</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E127" s="7">
         <v>0.99994995775740958</v>
@@ -10777,7 +10933,7 @@
         <v>2.753333159056182</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E128" s="5">
         <v>0.99997315191721281</v>
@@ -10794,7 +10950,7 @@
         <v>2.7533332417797731</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E129" s="7">
         <v>0.99998589580811603</v>
@@ -10811,7 +10967,7 @@
         <v>2.753333286241614</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E130" s="5">
         <v>0.99999274533120597</v>
@@ -10828,7 +10984,7 @@
         <v>2.753333309618168</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E131" s="7">
         <v>0.99999634658301095</v>
@@ -10845,7 +11001,7 @@
         <v>2.7533333216410449</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E132" s="5">
         <v>0.99999819875574003</v>
@@ -10862,7 +11018,7 @@
         <v>2.753333327689873</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E133" s="7">
         <v>0.99999913060206924</v>
@@ -10879,7 +11035,7 @@
         <v>2.7533333306668042</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E134" s="5">
         <v>0.99999958921036125</v>
@@ -10896,7 +11052,7 @@
         <v>2.7533333320999849</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E135" s="7">
         <v>0.99999980999775395</v>
@@ -10913,7 +11069,7 @@
         <v>2.7533333327749299</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E136" s="5">
         <v>0.9999999139757344</v>
@@ -10930,7 +11086,7 @@
         <v>2.7533333330858651</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E137" s="7">
         <v>0.99999996187658136</v>
@@ -10947,7 +11103,7 @@
         <v>2.7533333332259868</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E138" s="5">
         <v>0.99999998346295482</v>
@@ -10964,7 +11120,7 @@
         <v>2.753333333287757</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E139" s="7">
         <v>0.99999999297887598</v>
@@ -10981,7 +11137,7 @@
         <v>2.7533333333143939</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E140" s="5">
         <v>0.9999999970823964</v>
@@ -10998,7 +11154,7 @@
         <v>2.7533333333256311</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E141" s="7">
         <v>0.99999999881339596</v>
@@ -11015,7 +11171,7 @@
         <v>2.753333333330267</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E142" s="5">
         <v>0.99999999952768159</v>
@@ -11032,7 +11188,7 @@
         <v>2.7533333333321388</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E143" s="7">
         <v>0.99999999981600596</v>
@@ -11049,7 +11205,7 @@
         <v>2.7533333333328782</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E144" s="5">
         <v>0.999999999929854</v>
@@ -11066,7 +11222,7 @@
         <v>2.7533333333331629</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E145" s="7">
         <v>0.99999999997382882</v>
@@ -11083,7 +11239,7 @@
         <v>2.7533333333332708</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E146" s="5">
         <v>0.99999999999044442</v>
@@ -11100,7 +11256,7 @@
         <v>2.7533333333333112</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E147" s="7">
         <v>0.99999999999658562</v>
@@ -11117,7 +11273,7 @@
         <v>2.753333333333325</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E148" s="5">
         <v>0.99999999999880618</v>
@@ -11134,7 +11290,7 @@
         <v>2.7533333333333299</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E149" s="7">
         <v>0.99999999999959155</v>
@@ -11151,7 +11307,7 @@
         <v>2.7533333333333321</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E150" s="5">
         <v>0.99999999999986322</v>
@@ -11168,7 +11324,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E151" s="7">
         <v>0.99999999999995515</v>
@@ -11185,7 +11341,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E152" s="5">
         <v>0.99999999999998557</v>
@@ -11202,7 +11358,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E153" s="7">
         <v>0.99999999999999545</v>
@@ -11219,7 +11375,7 @@
         <v>2.753333333333333</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E154" s="5">
         <v>0.99999999999999878</v>
@@ -11233,7 +11389,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -11246,8 +11402,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>17</v>
+      <c r="A1" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -11256,19 +11412,19 @@
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -11282,7 +11438,7 @@
         <v>2.7533333004954281</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E4" s="5">
         <v>0.99999494118826204</v>
@@ -11299,7 +11455,7 @@
         <v>2.7533329940521911</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E5" s="7">
         <v>0.99994773243639723</v>
@@ -11316,7 +11472,7 @@
         <v>2.753330662629125</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E6" s="5">
         <v>0.99958857164419435</v>
@@ -11333,7 +11489,7 @@
         <v>2.7533172611289962</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E7" s="7">
         <v>0.99752417308316399</v>
@@ -11350,7 +11506,7 @@
         <v>2.753259032321929</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E8" s="5">
         <v>0.98855707481454158</v>
@@ -11367,7 +11523,7 @@
         <v>2.752805328501795</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E9" s="7">
         <v>0.95911502791321801</v>
@@ -11384,7 +11540,7 @@
         <v>2.5304860954410402</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E10" s="5">
         <v>0.88602957945290772</v>
@@ -11401,7 +11557,7 @@
         <v>2.377994760327526</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E11" s="7">
         <v>0.74884284696235781</v>
@@ -11418,7 +11574,7 @@
         <v>2.2511391734982551</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E12" s="5">
         <v>0.55409942029626791</v>
@@ -11435,7 +11591,7 @@
         <v>1.9852421601377661</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E13" s="7">
         <v>0.53108694825169667</v>
@@ -11452,7 +11608,7 @@
         <v>1.741718168991053</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E14" s="5">
         <v>0.55363876918689914</v>
@@ -11469,7 +11625,7 @@
         <v>1.5255612437651429</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E15" s="7">
         <v>0.45418844979280931</v>
@@ -11486,7 +11642,7 @@
         <v>1.287848230161682</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E16" s="5">
         <v>0.4149558591150827</v>
@@ -11503,7 +11659,7 @@
         <v>1.044729493868412</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E17" s="7">
         <v>0.4329082681818297</v>
@@ -11520,7 +11676,7 @@
         <v>0.82961213216864538</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E18" s="5">
         <v>0.60675550778505016</v>
@@ -11537,7 +11693,7 @@
         <v>0.60410539711971223</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E19" s="7">
         <v>0.75789821856308681</v>
@@ -11554,7 +11710,7 @@
         <v>0.48109606489361473</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E20" s="5">
         <v>0.86129356318733907</v>
@@ -11571,7 +11727,7 @@
         <v>0.37001191565913982</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E21" s="7">
         <v>0.90879602967725603</v>
@@ -11588,7 +11744,7 @@
         <v>0.3791007968506574</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E22" s="5">
         <v>0.90471416422207318</v>
@@ -11605,7 +11761,7 @@
         <v>0.46660078357776219</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E23" s="7">
         <v>0.85686299778276553</v>
@@ -11622,7 +11778,7 @@
         <v>0.56575668277196467</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E24" s="5">
         <v>0.77215855003762091</v>
@@ -11639,7 +11795,7 @@
         <v>0.79709535961653377</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E25" s="7">
         <v>0.65815522469845045</v>
@@ -11656,7 +11812,7 @@
         <v>0.9118787685815698</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E26" s="5">
         <v>0.52601751775214134</v>
@@ -11673,7 +11829,7 @@
         <v>1.024097502932416</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E27" s="7">
         <v>0.45936952453863927</v>
@@ -11690,7 +11846,7 @@
         <v>1.1347081924922899</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E28" s="5">
         <v>0.52732975953766736</v>
@@ -11707,7 +11863,7 @@
         <v>1.2622322676102939</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E29" s="7">
         <v>0.5613017690111779</v>
@@ -11724,7 +11880,7 @@
         <v>1.3515852924381271</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E30" s="5">
         <v>0.5583044455939995</v>
@@ -11741,7 +11897,7 @@
         <v>1.4512831846137</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E31" s="7">
         <v>0.52293370846870624</v>
@@ -11758,7 +11914,7 @@
         <v>1.5189387062893751</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E32" s="5">
         <v>0.46453091944837532</v>
@@ -11775,7 +11931,7 @@
         <v>1.593988629139214</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E33" s="7">
         <v>0.411190960502827</v>
@@ -11792,7 +11948,7 @@
         <v>1.677808434282245</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E34" s="5">
         <v>0.4451210257538169</v>
@@ -11809,7 +11965,7 @@
         <v>1.769156905497254</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E35" s="7">
         <v>0.46587640075135289</v>
@@ -11826,7 +11982,7 @@
         <v>1.864183299449121</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E36" s="5">
         <v>0.47198849533631709</v>
@@ -11843,7 +11999,7 @@
         <v>1.956649527073681</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E37" s="7">
         <v>0.46342603499464191</v>
@@ -11860,7 +12016,7 @@
         <v>2.041949832424784</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E38" s="5">
         <v>0.46370484279216462</v>
@@ -11877,7 +12033,7 @@
         <v>2.1188117065539251</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E39" s="7">
         <v>0.52779281623117025</v>
@@ -11894,7 +12050,7 @@
         <v>2.2730614728692542</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E40" s="5">
         <v>0.59116769671302904</v>
@@ -11911,7 +12067,7 @@
         <v>2.307530085890428</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E41" s="7">
         <v>0.65224063076552175</v>
@@ -11928,7 +12084,7 @@
         <v>2.3457112008511292</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E42" s="5">
         <v>0.70959565014259662</v>
@@ -11945,7 +12101,7 @@
         <v>2.3877004879653621</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E43" s="7">
         <v>0.76208667926799323</v>
@@ -11962,7 +12118,7 @@
         <v>2.4326704956994449</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E44" s="5">
         <v>0.80890218823707549</v>
@@ -11979,7 +12135,7 @@
         <v>2.479257968310093</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E45" s="7">
         <v>0.84959197454457769</v>
@@ -11996,7 +12152,7 @@
         <v>2.525627767837638</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E46" s="5">
         <v>0.88405648055256536</v>
@@ -12013,7 +12169,7 @@
         <v>2.5697888724568601</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E47" s="7">
         <v>0.9125043460352652</v>
@@ -12030,7 +12186,7 @@
         <v>2.6099775262322589</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E48" s="5">
         <v>0.93538762633117323</v>
@@ -12047,7 +12203,7 @@
         <v>2.7526634320121812</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E49" s="7">
         <v>0.95332578363380938</v>
@@ -12064,7 +12220,7 @@
         <v>2.7529588242982461</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E50" s="5">
         <v>0.96702918297450779</v>
@@ -12081,7 +12237,7 @@
         <v>2.753126591019853</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E51" s="7">
         <v>0.97723081656976918</v>
@@ -12098,7 +12254,7 @@
         <v>2.7532208527686932</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E52" s="5">
         <v>0.98463201471709838</v>
@@ -12115,7 +12271,7 @@
         <v>2.7532675252849441</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E53" s="7">
         <v>0.98986470734474397</v>
@@ -12132,7 +12288,7 @@
         <v>2.753290938261713</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E54" s="5">
         <v>0.99346998967043798</v>
@@ -12149,7 +12305,7 @@
         <v>2.7533066560937911</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E55" s="7">
         <v>0.99589070752148379</v>
@@ -12166,7 +12322,7 @@
         <v>2.753316939632279</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E56" s="5">
         <v>0.99747465172873517</v>
@@ -12183,7 +12339,7 @@
         <v>2.7533234965453302</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E57" s="7">
         <v>0.99848466335922637</v>
@@ -12200,7 +12356,7 @@
         <v>2.7533275708918481</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E58" s="5">
         <v>0.99911229326588402</v>
@@ -12217,7 +12373,7 @@
         <v>2.75333003814908</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E59" s="7">
         <v>0.99949237028832039</v>
@@ -12234,7 +12390,7 @@
         <v>2.7533314941652862</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E60" s="5">
         <v>0.9997166708187214</v>
@@ -12251,7 +12407,7 @@
         <v>2.7533323315239611</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E61" s="7">
         <v>0.99984566783158801</v>
@@ -12268,7 +12424,7 @@
         <v>2.7533328008225091</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E62" s="5">
         <v>0.99991796472573402</v>
@@ -12285,7 +12441,7 @@
         <v>2.753333057140162</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E63" s="7">
         <v>0.99995745136988679</v>
@@ -12302,7 +12458,7 @@
         <v>2.753333193566736</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E64" s="5">
         <v>0.99997846840129001</v>
@@ -12316,7 +12472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -12329,8 +12485,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>19</v>
+      <c r="A1" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -12339,19 +12495,19 @@
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -12365,7 +12521,7 @@
         <v>2.7530980830556908</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E4" s="5">
         <v>0.97499357812219123</v>
@@ -12382,7 +12538,7 @@
         <v>2.752916599882965</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E5" s="7">
         <v>0.96477675445345279</v>
@@ -12399,7 +12555,7 @@
         <v>2.7526152558394812</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E6" s="5">
         <v>0.95136184843388816</v>
@@ -12416,7 +12572,7 @@
         <v>2.6075650814850149</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E7" s="7">
         <v>0.93414321809213685</v>
@@ -12433,7 +12589,7 @@
         <v>2.5697559350893791</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E8" s="5">
         <v>0.91253848961729545</v>
@@ -12450,7 +12606,7 @@
         <v>2.5285226070805851</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E9" s="7">
         <v>0.886038953333395</v>
@@ -12467,7 +12623,7 @@
         <v>2.4854200333627219</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E10" s="5">
         <v>0.8542653114487343</v>
@@ -12484,7 +12640,7 @@
         <v>2.442150740941913</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E11" s="7">
         <v>0.81702314073339899</v>
@@ -12501,7 +12657,7 @@
         <v>2.400344128757923</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E12" s="5">
         <v>0.77435121411142505</v>
@@ -12518,7 +12674,7 @@
         <v>2.36128194062174</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E13" s="7">
         <v>0.72655551734497936</v>
@@ -12535,7 +12691,7 @@
         <v>2.3257680173792799</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E14" s="5">
         <v>0.67422263824352624</v>
@@ -12552,7 +12708,7 @@
         <v>2.293992636766248</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E15" s="7">
         <v>0.61820823048836471</v>
@@ -12569,7 +12725,7 @@
         <v>2.1150292105664819</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E16" s="5">
         <v>0.55959925078489137</v>
@@ -12586,7 +12742,7 @@
         <v>2.0297130239317789</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E17" s="7">
         <v>0.49965219369579772</v>
@@ -12603,7 +12759,7 @@
         <v>1.934810010931062</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E18" s="5">
         <v>0.43971300374727651</v>
@@ -12620,7 +12776,7 @@
         <v>1.8327410437805529</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E19" s="7">
         <v>0.39330740114172741</v>
@@ -12637,7 +12793,7 @@
         <v>1.727872933791937</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E20" s="5">
         <v>0.37527695963802171</v>
@@ -12654,7 +12810,7 @@
         <v>1.6278592305822479</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E21" s="7">
         <v>0.37356175793839641</v>
@@ -12671,7 +12827,7 @@
         <v>1.538325086481301</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E22" s="5">
         <v>0.44619506866953668</v>
@@ -12688,7 +12844,7 @@
         <v>1.4337146824235489</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E23" s="7">
         <v>0.50071780786304965</v>
@@ -12705,7 +12861,7 @@
         <v>1.334230813439802</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E24" s="5">
         <v>0.52130450688382268</v>
@@ -12722,7 +12878,7 @@
         <v>1.219376457438637</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E25" s="7">
         <v>0.49622823280758588</v>
@@ -12739,7 +12895,7 @@
         <v>1.082694374847083</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E26" s="5">
         <v>0.42527407132451678</v>
@@ -12756,7 +12912,7 @@
         <v>0.94038309586934377</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E27" s="7">
         <v>0.53460486524078399</v>
@@ -12773,7 +12929,7 @@
         <v>0.61341241327925733</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E28" s="5">
         <v>0.68897103058589304</v>
@@ -12790,7 +12946,7 @@
         <v>0.4898943821453951</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E29" s="7">
         <v>0.81567927232775939</v>
@@ -12807,7 +12963,7 @@
         <v>0.37633574518166668</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E30" s="5">
         <v>0.9040716658574468</v>
@@ -12824,7 +12980,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E31" s="7">
         <v>0.95647711432334759</v>
@@ -12841,7 +12997,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E32" s="5">
         <v>0.98288181434725885</v>
@@ -12858,7 +13014,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E33" s="7">
         <v>0.99418806497341961</v>
@@ -12875,7 +13031,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E34" s="5">
         <v>0.9983021721821902</v>
@@ -12889,8 +13045,326 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0.42735760446779553</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.90878878027413201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6">
+        <v>2</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0.61515561987812295</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0.74750746245307709</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0.88251463411941666</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6">
+        <v>2</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1.1062327076454881</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.58885220852162001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1.302781982315983</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.60025124154814513</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6">
+        <v>2</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1.507455604369089</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.47724986805182079</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1.6770681033276249</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.53280720734255593</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6">
+        <v>2</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1.8672406737734391</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.5888522085216199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2.0415871404252082</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.56375145854937825</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6">
+        <v>2</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2.2147090392842612</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4">
+        <v>2</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2.284674761667759</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0.63055865981823633</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="6">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6">
+        <v>2</v>
+      </c>
+      <c r="C15" s="7">
+        <v>2.3687885258069539</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.74750746245307709</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4">
+        <v>2</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2.466150891485849</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0.84134474606854293</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="6">
+        <v>13</v>
+      </c>
+      <c r="B17" s="6">
+        <v>2</v>
+      </c>
+      <c r="C17" s="7">
+        <v>2.5626322102036099</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.90878878027413201</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4">
+        <v>2</v>
+      </c>
+      <c r="C18" s="5">
+        <v>2.7526360551702811</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.95220964772718519</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="6">
+        <v>15</v>
+      </c>
+      <c r="B19" s="6">
+        <v>2</v>
+      </c>
+      <c r="C19" s="7">
+        <v>2.7531268337541128</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.97724986805182079</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -12902,8 +13376,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>21</v>
+      <c r="A1" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -12912,19 +13386,19 @@
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -12938,7 +13412,7 @@
         <v>0.45671809844851641</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E4" s="5">
         <v>0.86068174356051685</v>
@@ -12955,7 +13429,7 @@
         <v>0.51002102501585667</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E5" s="7">
         <v>0.81617628406796938</v>
@@ -12972,7 +13446,7 @@
         <v>0.56454303672666861</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E6" s="5">
         <v>0.7637416581980101</v>
@@ -12989,7 +13463,7 @@
         <v>0.76232212403810518</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E7" s="7">
         <v>0.70398330463531822</v>
@@ -13006,7 +13480,7 @@
         <v>0.82771219034110477</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E8" s="5">
         <v>0.6381031429537054</v>
@@ -13023,7 +13497,7 @@
         <v>0.88999060383393902</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E9" s="7">
         <v>0.56784667940862033</v>
@@ -13040,7 +13514,7 @@
         <v>0.94994802156866631</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E10" s="5">
         <v>0.49537079583518429</v>
@@ -13057,7 +13531,7 @@
         <v>1.009541254045988</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E11" s="7">
         <v>0.4253918039046839</v>
@@ -13074,7 +13548,7 @@
         <v>1.0691434005110341</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E12" s="5">
         <v>0.46891673139228751</v>
@@ -13091,7 +13565,7 @@
         <v>1.1275506178224279</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E13" s="7">
         <v>0.50511145677908975</v>
@@ -13108,7 +13582,7 @@
         <v>1.209655352644236</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E14" s="5">
         <v>0.53237343776393964</v>
@@ -13125,7 +13599,7 @@
         <v>1.2614904953994459</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E15" s="7">
         <v>0.54972368023450358</v>
@@ -13142,7 +13616,7 @@
         <v>1.309104515226911</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E16" s="5">
         <v>0.55684984382515412</v>
@@ -13159,7 +13633,7 @@
         <v>1.3531542582198279</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E17" s="7">
         <v>0.55406839149893417</v>
@@ -13176,7 +13650,7 @@
         <v>1.3944846997557889</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E18" s="5">
         <v>0.5422217848158406</v>
@@ -13193,7 +13667,7 @@
         <v>1.452637745414076</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E19" s="7">
         <v>0.52253543066138985</v>
@@ -13210,7 +13684,7 @@
         <v>1.4848215097696491</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E20" s="5">
         <v>0.4964613708003458</v>
@@ -13227,7 +13701,7 @@
         <v>1.5184726863857001</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E21" s="7">
         <v>0.46553222520960708</v>
@@ -13244,7 +13718,7 @@
         <v>1.5538288373966169</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E22" s="5">
         <v>0.43124164797838699</v>
@@ -13261,7 +13735,7 @@
         <v>1.5909982766151589</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E23" s="7">
         <v>0.42948131606715628</v>
@@ -13278,7 +13752,7 @@
         <v>1.630071930632764</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E24" s="5">
         <v>0.45129756780541042</v>
@@ -13295,7 +13769,7 @@
         <v>1.6711154561633039</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E25" s="7">
         <v>0.4703905698429412</v>
@@ -13312,7 +13786,7 @@
         <v>1.713706323449784</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E26" s="5">
         <v>0.48642067052010651</v>
@@ -13329,7 +13803,7 @@
         <v>1.7574068785729731</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E27" s="7">
         <v>0.49912064421681501</v>
@@ -13346,7 +13820,7 @@
         <v>1.8017578337527089</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E28" s="5">
         <v>0.50830295495903299</v>
@@ -13363,7 +13837,7 @@
         <v>1.8462422806189911</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E29" s="7">
         <v>0.51386349390776154</v>
@@ -13380,7 +13854,7 @@
         <v>1.890409297677716</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E30" s="5">
         <v>0.51578177193482622</v>
@@ -13397,7 +13871,7 @@
         <v>1.933664307465139</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E31" s="7">
         <v>0.51411776626515449</v>
@@ -13414,7 +13888,7 @@
         <v>1.9751158295282529</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E32" s="5">
         <v>0.50900580812420038</v>
@@ -13431,7 +13905,7 @@
         <v>2.014432568949978</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E33" s="7">
         <v>0.50064604330933937</v>
@@ -13448,7 +13922,7 @@
         <v>2.0514840260197582</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E34" s="5">
         <v>0.48929409159667742</v>
@@ -13465,7 +13939,7 @@
         <v>2.0862458354414759</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E35" s="7">
         <v>0.47524957140784929</v>
@@ -13482,7 +13956,7 @@
         <v>2.1187544867096602</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E36" s="5">
         <v>0.48901330636798568</v>
@@ -13499,7 +13973,7 @@
         <v>2.2291500358275238</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E37" s="7">
         <v>0.51780809484982349</v>
@@ -13516,7 +13990,7 @@
         <v>2.2431937537629021</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E38" s="5">
         <v>0.54651024485083188</v>
@@ -13533,7 +14007,7 @@
         <v>2.2577117695275151</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E39" s="7">
         <v>0.57497138434682737</v>
@@ -13550,7 +14024,7 @@
         <v>2.2727945412180408</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E40" s="5">
         <v>0.60304688147781815</v>
@@ -13567,7 +14041,7 @@
         <v>2.288471894281479</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E41" s="7">
         <v>0.63059804491983928</v>
@@ -13584,7 +14058,7 @@
         <v>2.304788020219164</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E42" s="5">
         <v>0.65749417201065563</v>
@@ -13601,7 +14075,7 @@
         <v>2.3219021751425459</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E43" s="7">
         <v>0.68361439440580962</v>
@@ -13618,7 +14092,7 @@
         <v>2.3399299778604088</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E44" s="5">
         <v>0.70884927821189192</v>
@@ -13635,7 +14109,7 @@
         <v>2.3587756186403168</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E45" s="7">
         <v>0.73310214410596619</v>
@@ -13652,7 +14126,7 @@
         <v>2.378334946897203</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E46" s="5">
         <v>0.75629008252076513</v>
@@ -13669,7 +14143,7 @@
         <v>2.3986034819383129</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E47" s="7">
         <v>0.77834464913534962</v>
@@ -13686,7 +14160,7 @@
         <v>2.4193613150329472</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E48" s="5">
         <v>0.79921223622724324</v>
@@ -13703,7 +14177,7 @@
         <v>2.4405206442132301</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E49" s="7">
         <v>0.81885412549006142</v>
@@ -13720,7 +14194,7 @@
         <v>2.461873634466329</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E50" s="5">
         <v>0.83724623730552894</v>
@@ -13737,7 +14211,7 @@
         <v>2.4832854232825619</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E51" s="7">
         <v>0.85437859983406872</v>
@@ -13754,7 +14228,7 @@
         <v>2.504561851306391</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E52" s="5">
         <v>0.87025456837085235</v>
@@ -13771,7 +14245,7 @@
         <v>2.5255127881940909</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E53" s="7">
         <v>0.88488983099562191</v>
@@ -13788,7 +14262,7 @@
         <v>2.5459625950817029</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E54" s="5">
         <v>0.89831124049640398</v>
@@ -13805,7 +14279,7 @@
         <v>2.565742346486195</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E55" s="7">
         <v>0.91055551482282082</v>
@@ -13822,7 +14296,7 @@
         <v>2.5846945682912432</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E56" s="5">
         <v>0.92166784895591658</v>
@@ -13839,7 +14313,7 @@
         <v>2.6027002018970018</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E57" s="7">
         <v>0.9317004801712484</v>
@@ -13856,7 +14330,7 @@
         <v>2.6196583407615091</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E58" s="5">
         <v>0.94071124638394077</v>
@@ -13873,7 +14347,7 @@
         <v>2.6354438048221049</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E59" s="7">
         <v>0.94876217380938277</v>
@@ -13890,7 +14364,7 @@
         <v>2.7527269927007372</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E60" s="5">
         <v>0.95591812579504198</v>
@@ -13907,7 +14381,7 @@
         <v>2.752869131336912</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E61" s="7">
         <v>0.96224553963910442</v>
@@ -13924,7 +14398,7 @@
         <v>2.7529734819715679</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E62" s="5">
         <v>0.9678112727752376</v>
@@ -13941,7 +14415,7 @@
         <v>2.7530647188025759</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E63" s="7">
         <v>0.97268157412457801</v>
@@ -13958,7 +14432,7 @@
         <v>2.753122646022224</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E64" s="5">
         <v>0.97692119092955398</v>
@@ -13975,7 +14449,7 @@
         <v>2.75316941604915</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E65" s="7">
         <v>0.9805926161923888</v>
@@ -13992,7 +14466,7 @@
         <v>2.7532096930107142</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E66" s="5">
         <v>0.98375547711040923</v>
@@ -14009,7 +14483,7 @@
         <v>2.753244199843329</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E67" s="7">
         <v>0.98646606075641818</v>
@@ -14026,7 +14500,7 @@
         <v>2.7532604605620801</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E68" s="5">
         <v>0.98877696977980045</v>
@@ -14043,7 +14517,7 @@
         <v>2.7532731897656202</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E69" s="7">
         <v>0.99073689814685262</v>
@@ -14060,7 +14534,7 @@
         <v>2.7532839285367889</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E70" s="5">
         <v>0.99239051490433083</v>
@@ -14077,7 +14551,7 @@
         <v>2.75329294117217</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E71" s="7">
         <v>0.99377844261336301</v>
@@ -14094,7 +14568,7 @@
         <v>2.753300465920629</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E72" s="5">
         <v>0.99493731641031602</v>
@@ -14111,7 +14585,7 @@
         <v>2.7533067158390692</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E73" s="7">
         <v>0.99589990953541363</v>
@@ -14128,7 +14602,7 @@
         <v>2.7533118799811618</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E74" s="5">
         <v>0.99669531154375979</v>
@@ -14145,7 +14619,7 @@
         <v>2.7533161248361822</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E75" s="7">
         <v>0.9973491461842896</v>
@@ -14162,7 +14636,7 @@
         <v>2.7533195959418562</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E76" s="5">
         <v>0.99788381700557682</v>
@@ -14179,7 +14653,7 @@
         <v>2.753322419603315</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E77" s="7">
         <v>0.99831877003170721</v>
@@ -14196,7 +14670,7 @@
         <v>2.7533247046591671</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E78" s="5">
         <v>0.9986707642617092</v>
@@ -14213,7 +14687,7 @@
         <v>2.7533265442450161</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E79" s="7">
         <v>0.99895414220694201</v>
@@ -14230,7 +14704,7 @@
         <v>2.7533280175139958</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E80" s="5">
         <v>0.99918109412841716</v>
@@ -14247,7 +14721,7 @@
         <v>2.7533291912826732</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E81" s="7">
         <v>0.99936191101859995</v>
@@ -14264,7 +14738,7 @@
         <v>2.753330121578895</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E82" s="5">
         <v>0.99950522265061637</v>
@@ -14281,7 +14755,7 @@
         <v>2.7533308550754678</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E83" s="7">
         <v>0.99961821816462915</v>
